--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الطلاب" sheetId="1" r:id="rId1"/>
     <sheet name="درجات الفصل الأول" sheetId="2" r:id="rId2"/>
-    <sheet name="ورقة3" sheetId="3" r:id="rId3"/>
+    <sheet name="درجات الفصل الثاني" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
   <si>
     <t>رقم الطالبة</t>
   </si>
@@ -166,13 +166,25 @@
   </si>
   <si>
     <t>اختبار نهاية الفصل الكلي</t>
+  </si>
+  <si>
+    <t>السجل الشامل لدرجات وحالة أداء الطالبات - الفصل الدراسي الأول</t>
+  </si>
+  <si>
+    <t>نوهان ثروت علي</t>
+  </si>
+  <si>
+    <t>2026 - 2026</t>
+  </si>
+  <si>
+    <t>السجل الشامل لدرجات وحالة أداء الطالبات - الفصل الدراسي الثاني</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +213,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -216,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -261,11 +287,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -273,116 +319,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="17">
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -414,7 +389,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -429,6 +404,30 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -670,16 +669,62 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="medium">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
           <color rgb="FFC4C7C5"/>
-        </top>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -693,18 +738,92 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:G16" totalsRowShown="0" headerRowDxfId="10" dataDxfId="11" headerRowBorderDxfId="19" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:G16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A2:G16"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="رقم الطالبة" dataDxfId="18"/>
-    <tableColumn id="2" name="اسم الطالبة" dataDxfId="17"/>
-    <tableColumn id="3" name="السنة الدراسية" dataDxfId="16"/>
-    <tableColumn id="4" name="الصف الدراسي" dataDxfId="15"/>
-    <tableColumn id="5" name="الفصل" dataDxfId="14"/>
-    <tableColumn id="6" name="المادة" dataDxfId="13"/>
-    <tableColumn id="7" name="اسم المعلمة" dataDxfId="12"/>
+    <tableColumn id="1" name="رقم الطالبة" dataDxfId="12"/>
+    <tableColumn id="2" name="اسم الطالبة" dataDxfId="11"/>
+    <tableColumn id="3" name="السنة الدراسية" dataDxfId="10"/>
+    <tableColumn id="4" name="الصف الدراسي" dataDxfId="9"/>
+    <tableColumn id="5" name="الفصل" dataDxfId="8"/>
+    <tableColumn id="6" name="المادة" dataDxfId="7"/>
+    <tableColumn id="7" name="اسم المعلمة" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="الجدول1" displayName="الجدول1" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="5">
+  <autoFilter ref="A3:AB411"/>
+  <tableColumns count="28">
+    <tableColumn id="1" name="رقم"/>
+    <tableColumn id="2" name="الطالبة"/>
+    <tableColumn id="3" name="الصف الدراسي"/>
+    <tableColumn id="4" name="الفصل"/>
+    <tableColumn id="5" name="المادة"/>
+    <tableColumn id="6" name="كويز 1"/>
+    <tableColumn id="7" name="كويز 1 الكلي"/>
+    <tableColumn id="8" name="كويز 2"/>
+    <tableColumn id="9" name="كويز 2 الكلي"/>
+    <tableColumn id="10" name="كويز 3"/>
+    <tableColumn id="11" name="كويز 3 الكلي"/>
+    <tableColumn id="12" name="كويز 4"/>
+    <tableColumn id="13" name="كويز 4 الكلي"/>
+    <tableColumn id="14" name="كويز 5"/>
+    <tableColumn id="15" name="كويز 5 الكلي"/>
+    <tableColumn id="16" name="الفترة الأولى"/>
+    <tableColumn id="17" name="الفترة الأولى الكلي"/>
+    <tableColumn id="18" name="الفترة الثانية"/>
+    <tableColumn id="19" name="الفترة الثانية الكلي"/>
+    <tableColumn id="20" name="اختبار التحسين"/>
+    <tableColumn id="21" name="اختبار التحسين الكلي"/>
+    <tableColumn id="22" name="اختبار نهاية الفصل"/>
+    <tableColumn id="23" name="اختبار نهاية الفصل الكلي"/>
+    <tableColumn id="24" name="المجموع المستحق"/>
+    <tableColumn id="25" name="المجموع الكلي"/>
+    <tableColumn id="26" name="النسبة المئوية"/>
+    <tableColumn id="27" name="التقدير العام"/>
+    <tableColumn id="28" name="حالة الخطة العلاجية"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="الجدول13" displayName="الجدول13" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="A3:AB411"/>
+  <tableColumns count="28">
+    <tableColumn id="1" name="رقم"/>
+    <tableColumn id="2" name="الطالبة"/>
+    <tableColumn id="3" name="الصف الدراسي"/>
+    <tableColumn id="4" name="الفصل"/>
+    <tableColumn id="5" name="المادة"/>
+    <tableColumn id="6" name="كويز 1"/>
+    <tableColumn id="7" name="كويز 1 الكلي"/>
+    <tableColumn id="8" name="كويز 2"/>
+    <tableColumn id="9" name="كويز 2 الكلي"/>
+    <tableColumn id="10" name="كويز 3"/>
+    <tableColumn id="11" name="كويز 3 الكلي"/>
+    <tableColumn id="12" name="كويز 4"/>
+    <tableColumn id="13" name="كويز 4 الكلي"/>
+    <tableColumn id="14" name="كويز 5"/>
+    <tableColumn id="15" name="كويز 5 الكلي"/>
+    <tableColumn id="16" name="الفترة الأولى"/>
+    <tableColumn id="17" name="الفترة الأولى الكلي"/>
+    <tableColumn id="18" name="الفترة الثانية"/>
+    <tableColumn id="19" name="الفترة الثانية الكلي"/>
+    <tableColumn id="20" name="اختبار التحسين"/>
+    <tableColumn id="21" name="اختبار التحسين الكلي"/>
+    <tableColumn id="22" name="اختبار نهاية الفصل"/>
+    <tableColumn id="23" name="اختبار نهاية الفصل الكلي"/>
+    <tableColumn id="24" name="المجموع المستحق"/>
+    <tableColumn id="25" name="المجموع الكلي"/>
+    <tableColumn id="26" name="النسبة المئوية"/>
+    <tableColumn id="27" name="التقدير العام"/>
+    <tableColumn id="28" name="حالة الخطة العلاجية"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1008,36 +1127,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1271,9 +1390,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1011</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1313,112 +1453,151 @@
   <dimension ref="A2:AG37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
     <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="12.21875" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="17.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" customWidth="1"/>
+    <col min="23" max="23" width="20.109375" customWidth="1"/>
+    <col min="24" max="24" width="15.88671875" customWidth="1"/>
+    <col min="25" max="25" width="13.33203125" customWidth="1"/>
+    <col min="26" max="26" width="13.21875" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" customWidth="1"/>
+    <col min="28" max="28" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:33" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="2" spans="1:33" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+    </row>
+    <row r="3" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="M3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="N3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="O3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="P3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="Q3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="R3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="S3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="T3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="U3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="V3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="W3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="X3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="Y3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="Z3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AA3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AB3" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
     </row>
     <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -1441,16 +1620,80 @@
         <f>'معلومات الطلاب'!F4</f>
         <v>رياضيات</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="P4" s="2"/>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2">
+        <v>4</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>20</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="6">
+        <v>20</v>
+      </c>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>0</v>
+      </c>
+      <c r="V4" s="6">
+        <v>35</v>
+      </c>
+      <c r="W4" s="7">
+        <v>40</v>
+      </c>
+      <c r="X4">
+        <f>F4+H4+J4+L4+N4+P4+R4+T4+V4</f>
+        <v>88</v>
+      </c>
+      <c r="Y4">
+        <f>G4+I4+K4+M4+O4+Q4+S4+U4+W4</f>
+        <v>100</v>
+      </c>
+      <c r="Z4">
+        <f>X4/Y4</f>
+        <v>0.88</v>
+      </c>
+      <c r="AA4" t="str">
+        <f>IF(Z4&gt;=0.9,"ممتاز",IF(Z4&gt;=0.8,"جيد جداً",IF(Z4&gt;=0.7,"جيد",IF(Z4&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v>جيد جداً</v>
+      </c>
+      <c r="AB4" t="str">
+        <f>IF(Z4&lt;0.6,"متعثر",IF(Z4&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
+        <v>لا يحتاج متابعة</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -1473,16 +1716,80 @@
         <f>'معلومات الطلاب'!F5</f>
         <v>رياضيات</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="P5" s="2"/>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>5</v>
+      </c>
+      <c r="L5" s="2">
+        <v>5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>20</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="6">
+        <v>20</v>
+      </c>
+      <c r="T5" s="6">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6">
+        <v>33</v>
+      </c>
+      <c r="W5" s="7">
+        <v>40</v>
+      </c>
+      <c r="X5">
+        <f t="shared" ref="X5:X13" si="0">F5+H5+J5+L5+N5+P5+R5+T5+V5</f>
+        <v>77</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" ref="Y5:Y13" si="1">G5+I5+K5+M5+O5+Q5+S5+U5+W5</f>
+        <v>100</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" ref="Z5:Z13" si="2">X5/Y5</f>
+        <v>0.77</v>
+      </c>
+      <c r="AA5" t="str">
+        <f t="shared" ref="AA5:AA13" si="3">IF(Z5&gt;=0.9,"ممتاز",IF(Z5&gt;=0.8,"جيد جداً",IF(Z5&gt;=0.7,"جيد",IF(Z5&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v>جيد</v>
+      </c>
+      <c r="AB5" t="str">
+        <f t="shared" ref="AB5:AB13" si="4">IF(Z5&lt;0.6,"متعثر",IF(Z5&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
+        <v>محتاج متابعة</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -1505,16 +1812,80 @@
         <f>'معلومات الطلاب'!F6</f>
         <v>رياضيات</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="P6" s="2"/>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2">
+        <v>5</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>20</v>
+      </c>
+      <c r="R6" s="5">
+        <v>15</v>
+      </c>
+      <c r="S6" s="6">
+        <v>20</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6">
+        <v>15</v>
+      </c>
+      <c r="W6" s="7">
+        <v>40</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="2"/>
+        <v>0.46</v>
+      </c>
+      <c r="AA6" t="str">
+        <f t="shared" si="3"/>
+        <v>ضعيف</v>
+      </c>
+      <c r="AB6" t="str">
+        <f t="shared" si="4"/>
+        <v>متعثر</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -1537,16 +1908,80 @@
         <f>'معلومات الطلاب'!F7</f>
         <v>رياضيات</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="F7" s="2">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>20</v>
+      </c>
+      <c r="R7" s="7">
+        <v>10</v>
+      </c>
+      <c r="S7" s="6">
+        <v>20</v>
+      </c>
+      <c r="T7" s="6">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6">
+        <v>0</v>
+      </c>
+      <c r="V7" s="7">
+        <v>33</v>
+      </c>
+      <c r="W7" s="7">
+        <v>40</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="2"/>
+        <v>0.59</v>
+      </c>
+      <c r="AA7" t="str">
+        <f t="shared" si="3"/>
+        <v>ضعيف</v>
+      </c>
+      <c r="AB7" t="str">
+        <f t="shared" si="4"/>
+        <v>متعثر</v>
+      </c>
     </row>
     <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -1569,16 +2004,80 @@
         <f>'معلومات الطلاب'!F8</f>
         <v>علوم</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="P8" s="2"/>
+      <c r="F8" s="2">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2</v>
+      </c>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>20</v>
+      </c>
+      <c r="R8" s="7">
+        <v>18</v>
+      </c>
+      <c r="S8" s="6">
+        <v>20</v>
+      </c>
+      <c r="T8" s="6">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7">
+        <v>33</v>
+      </c>
+      <c r="W8" s="7">
+        <v>40</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="2"/>
+        <v>0.73</v>
+      </c>
+      <c r="AA8" t="str">
+        <f t="shared" si="3"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB8" t="str">
+        <f t="shared" si="4"/>
+        <v>محتاج متابعة</v>
+      </c>
     </row>
     <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -1601,16 +2100,80 @@
         <f>'معلومات الطلاب'!F9</f>
         <v>علوم</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="P9" s="2"/>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>20</v>
+      </c>
+      <c r="R9" s="7">
+        <v>5</v>
+      </c>
+      <c r="S9" s="6">
+        <v>20</v>
+      </c>
+      <c r="T9" s="6">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7">
+        <v>33</v>
+      </c>
+      <c r="W9" s="7">
+        <v>40</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="AA9" t="str">
+        <f t="shared" si="3"/>
+        <v>مقبول</v>
+      </c>
+      <c r="AB9" t="str">
+        <f t="shared" si="4"/>
+        <v>محتاج متابعة</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -1633,16 +2196,80 @@
         <f>'معلومات الطلاب'!F10</f>
         <v>علوم</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2">
+        <v>3</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2">
+        <v>5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>20</v>
+      </c>
+      <c r="R10" s="7">
+        <v>11</v>
+      </c>
+      <c r="S10" s="6">
+        <v>20</v>
+      </c>
+      <c r="T10" s="6">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6">
+        <v>0</v>
+      </c>
+      <c r="V10" s="7">
+        <v>33</v>
+      </c>
+      <c r="W10" s="7">
+        <v>40</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="2"/>
+        <v>0.69</v>
+      </c>
+      <c r="AA10" t="str">
+        <f t="shared" si="3"/>
+        <v>مقبول</v>
+      </c>
+      <c r="AB10" t="str">
+        <f t="shared" si="4"/>
+        <v>محتاج متابعة</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -1665,16 +2292,80 @@
         <f>'معلومات الطلاب'!F11</f>
         <v>علوم</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="F11" s="2">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>5</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>20</v>
+      </c>
+      <c r="R11" s="7">
+        <v>20</v>
+      </c>
+      <c r="S11" s="6">
+        <v>20</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0</v>
+      </c>
+      <c r="V11" s="7">
+        <v>33</v>
+      </c>
+      <c r="W11" s="7">
+        <v>40</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="2"/>
+        <v>0.68</v>
+      </c>
+      <c r="AA11" t="str">
+        <f t="shared" si="3"/>
+        <v>مقبول</v>
+      </c>
+      <c r="AB11" t="str">
+        <f t="shared" si="4"/>
+        <v>محتاج متابعة</v>
+      </c>
     </row>
     <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -1697,392 +2388,2184 @@
         <f>'معلومات الطلاب'!F12</f>
         <v>علوم</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="P12" s="2"/>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>3</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>20</v>
+      </c>
+      <c r="R12" s="7">
+        <v>13</v>
+      </c>
+      <c r="S12" s="6">
+        <v>20</v>
+      </c>
+      <c r="T12" s="6">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6">
+        <v>0</v>
+      </c>
+      <c r="V12" s="7">
+        <v>33</v>
+      </c>
+      <c r="W12" s="7">
+        <v>40</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="AA12" t="str">
+        <f t="shared" si="3"/>
+        <v>مقبول</v>
+      </c>
+      <c r="AB12" t="str">
+        <f t="shared" si="4"/>
+        <v>محتاج متابعة</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="26" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="14:23" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="V27" s="1" t="s">
+      <c r="A13">
+        <f>'معلومات الطلاب'!A13</f>
+        <v>1011</v>
+      </c>
+      <c r="B13" t="str">
+        <f>'معلومات الطلاب'!B13</f>
+        <v>نوهان ثروت علي</v>
+      </c>
+      <c r="C13" t="str">
+        <f>'معلومات الطلاب'!D13</f>
+        <v>السادس</v>
+      </c>
+      <c r="D13">
+        <f>'معلومات الطلاب'!E13</f>
+        <v>2</v>
+      </c>
+      <c r="E13" t="str">
+        <f>'معلومات الطلاب'!F13</f>
+        <v>علوم</v>
+      </c>
+      <c r="F13" s="2">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>5</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2</v>
+      </c>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>20</v>
+      </c>
+      <c r="R13" s="7">
+        <v>15</v>
+      </c>
+      <c r="S13" s="6">
+        <v>20</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0</v>
+      </c>
+      <c r="V13" s="7">
         <v>33</v>
       </c>
-      <c r="W27" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N28" s="2">
-        <v>5</v>
-      </c>
-      <c r="O28" s="2">
-        <v>5</v>
-      </c>
-      <c r="P28" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>5</v>
-      </c>
-      <c r="R28" s="2">
-        <v>5</v>
-      </c>
-      <c r="S28" s="2">
-        <v>18</v>
-      </c>
-      <c r="T28" s="2">
-        <v>19</v>
-      </c>
-      <c r="U28" s="2">
-        <v>20</v>
-      </c>
-      <c r="V28" s="2">
-        <v>38</v>
-      </c>
-      <c r="W28" s="2">
+      <c r="W13" s="7">
+        <v>40</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N29" s="2">
-        <v>4</v>
-      </c>
-      <c r="O29" s="2">
-        <v>3</v>
-      </c>
-      <c r="P29" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>4</v>
-      </c>
-      <c r="R29" s="2">
-        <v>4</v>
-      </c>
-      <c r="S29" s="2">
-        <v>15</v>
-      </c>
-      <c r="T29" s="2">
-        <v>14</v>
-      </c>
-      <c r="U29" s="2">
-        <v>16</v>
-      </c>
-      <c r="V29" s="2">
-        <v>32</v>
-      </c>
-      <c r="W29" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N30" s="2">
-        <v>2</v>
-      </c>
-      <c r="O30" s="2">
-        <v>3</v>
-      </c>
-      <c r="P30" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>3</v>
-      </c>
-      <c r="R30" s="2">
-        <v>2</v>
-      </c>
-      <c r="S30" s="2">
-        <v>10</v>
-      </c>
-      <c r="T30" s="2">
-        <v>9</v>
-      </c>
-      <c r="U30" s="2">
-        <v>12</v>
-      </c>
-      <c r="V30" s="2">
-        <v>22</v>
-      </c>
-      <c r="W30" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N31" s="2">
-        <v>5</v>
-      </c>
-      <c r="O31" s="2">
-        <v>4</v>
-      </c>
-      <c r="P31" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>5</v>
-      </c>
-      <c r="R31" s="2">
-        <v>4</v>
-      </c>
-      <c r="S31" s="2">
-        <v>17</v>
-      </c>
-      <c r="T31" s="2">
-        <v>18</v>
-      </c>
-      <c r="U31" s="2">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2">
-        <v>36</v>
-      </c>
-      <c r="W31" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N32" s="2">
-        <v>3</v>
-      </c>
-      <c r="O32" s="2">
-        <v>2</v>
-      </c>
-      <c r="P32" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>4</v>
-      </c>
-      <c r="R32" s="2">
-        <v>3</v>
-      </c>
-      <c r="S32" s="2">
-        <v>12</v>
-      </c>
-      <c r="T32" s="2">
-        <v>11</v>
-      </c>
-      <c r="U32" s="2">
-        <v>15</v>
-      </c>
-      <c r="V32" s="2">
-        <v>28</v>
-      </c>
-      <c r="W32" s="2">
-        <v>100</v>
-      </c>
+      <c r="Z13">
+        <f t="shared" si="2"/>
+        <v>0.72</v>
+      </c>
+      <c r="AA13" t="str">
+        <f t="shared" si="3"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB13" t="str">
+        <f t="shared" si="4"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f>'معلومات الطلاب'!A14</f>
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <f>'معلومات الطلاب'!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f>'معلومات الطلاب'!D14</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>'معلومات الطلاب'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>'معلومات الطلاب'!F14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f>'معلومات الطلاب'!A15</f>
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <f>'معلومات الطلاب'!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f>'معلومات الطلاب'!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>'معلومات الطلاب'!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>'معلومات الطلاب'!F15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f>'معلومات الطلاب'!A16</f>
+        <v>0</v>
+      </c>
+      <c r="B16">
+        <f>'معلومات الطلاب'!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f>'معلومات الطلاب'!D16</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f>'معلومات الطلاب'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>'معلومات الطلاب'!F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f>'معلومات الطلاب'!A17</f>
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <f>'معلومات الطلاب'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f>'معلومات الطلاب'!D17</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f>'معلومات الطلاب'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>'معلومات الطلاب'!F17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f>'معلومات الطلاب'!A18</f>
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <f>'معلومات الطلاب'!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f>'معلومات الطلاب'!D18</f>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f>'معلومات الطلاب'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f>'معلومات الطلاب'!F18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f>'معلومات الطلاب'!A19</f>
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <f>'معلومات الطلاب'!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f>'معلومات الطلاب'!D19</f>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f>'معلومات الطلاب'!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f>'معلومات الطلاب'!F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f>'معلومات الطلاب'!A20</f>
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <f>'معلومات الطلاب'!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f>'معلومات الطلاب'!D20</f>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f>'معلومات الطلاب'!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f>'معلومات الطلاب'!F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f>'معلومات الطلاب'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="B21">
+        <f>'معلومات الطلاب'!B21</f>
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <f>'معلومات الطلاب'!D21</f>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f>'معلومات الطلاب'!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f>'معلومات الطلاب'!F21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f>'معلومات الطلاب'!A22</f>
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <f>'معلومات الطلاب'!B22</f>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f>'معلومات الطلاب'!D22</f>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f>'معلومات الطلاب'!E22</f>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>'معلومات الطلاب'!F22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f>'معلومات الطلاب'!A23</f>
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <f>'معلومات الطلاب'!B23</f>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f>'معلومات الطلاب'!D23</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>'معلومات الطلاب'!E23</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>'معلومات الطلاب'!F23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f>'معلومات الطلاب'!A24</f>
+        <v>0</v>
+      </c>
+      <c r="B24">
+        <f>'معلومات الطلاب'!B24</f>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f>'معلومات الطلاب'!D24</f>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f>'معلومات الطلاب'!E24</f>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>'معلومات الطلاب'!F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f>'معلومات الطلاب'!A25</f>
+        <v>0</v>
+      </c>
+      <c r="B25">
+        <f>'معلومات الطلاب'!B25</f>
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <f>'معلومات الطلاب'!D25</f>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f>'معلومات الطلاب'!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f>'معلومات الطلاب'!F25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <f>'معلومات الطلاب'!A26</f>
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <f>'معلومات الطلاب'!B26</f>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <f>'معلومات الطلاب'!D26</f>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>'معلومات الطلاب'!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>'معلومات الطلاب'!F26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <f>'معلومات الطلاب'!A27</f>
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <f>'معلومات الطلاب'!B27</f>
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <f>'معلومات الطلاب'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f>'معلومات الطلاب'!E27</f>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f>'معلومات الطلاب'!F27</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+    </row>
+    <row r="29" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+    </row>
+    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+    </row>
+    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+    </row>
+    <row r="32" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
     </row>
     <row r="33" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="2">
-        <v>5</v>
-      </c>
-      <c r="P33" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>5</v>
-      </c>
-      <c r="R33" s="2">
-        <v>5</v>
-      </c>
-      <c r="S33" s="2">
-        <v>20</v>
-      </c>
-      <c r="T33" s="2">
-        <v>20</v>
-      </c>
-      <c r="U33" s="2">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2">
-        <v>40</v>
-      </c>
-      <c r="W33" s="2">
-        <v>100</v>
-      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
     </row>
     <row r="34" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N34" s="2">
-        <v>4</v>
-      </c>
-      <c r="O34" s="2">
-        <v>4</v>
-      </c>
-      <c r="P34" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>4</v>
-      </c>
-      <c r="R34" s="2">
-        <v>4</v>
-      </c>
-      <c r="S34" s="2">
-        <v>16</v>
-      </c>
-      <c r="T34" s="2">
-        <v>15</v>
-      </c>
-      <c r="U34" s="2">
-        <v>18</v>
-      </c>
-      <c r="V34" s="2">
-        <v>33</v>
-      </c>
-      <c r="W34" s="2">
-        <v>100</v>
-      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
     </row>
     <row r="35" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N35" s="2">
-        <v>1</v>
-      </c>
-      <c r="O35" s="2">
-        <v>2</v>
-      </c>
-      <c r="P35" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>1</v>
-      </c>
-      <c r="R35" s="2">
-        <v>2</v>
-      </c>
-      <c r="S35" s="2">
-        <v>8</v>
-      </c>
-      <c r="T35" s="2">
-        <v>7</v>
-      </c>
-      <c r="U35" s="2">
-        <v>10</v>
-      </c>
-      <c r="V35" s="2">
-        <v>18</v>
-      </c>
-      <c r="W35" s="2">
-        <v>100</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
     </row>
     <row r="36" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N36" s="2">
-        <v>5</v>
-      </c>
-      <c r="O36" s="2">
-        <v>4</v>
-      </c>
-      <c r="P36" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q36" s="2">
-        <v>5</v>
-      </c>
-      <c r="R36" s="2">
-        <v>4</v>
-      </c>
-      <c r="S36" s="2">
-        <v>18</v>
-      </c>
-      <c r="T36" s="2">
-        <v>17</v>
-      </c>
-      <c r="U36" s="2">
-        <v>0</v>
-      </c>
-      <c r="V36" s="2">
-        <v>35</v>
-      </c>
-      <c r="W36" s="2">
-        <v>100</v>
-      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
     </row>
     <row r="37" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N37" s="2">
-        <v>4</v>
-      </c>
-      <c r="O37" s="2">
-        <v>3</v>
-      </c>
-      <c r="P37" s="2">
-        <v>4</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>4</v>
-      </c>
-      <c r="R37" s="2">
-        <v>3</v>
-      </c>
-      <c r="S37" s="2">
-        <v>14</v>
-      </c>
-      <c r="T37" s="2">
-        <v>13</v>
-      </c>
-      <c r="U37" s="2">
-        <v>16</v>
-      </c>
-      <c r="V37" s="2">
-        <v>30</v>
-      </c>
-      <c r="W37" s="2">
-        <v>100</v>
-      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:AB2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A2:AG37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="12.21875" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="17.6640625" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" customWidth="1"/>
+    <col min="23" max="23" width="20.109375" customWidth="1"/>
+    <col min="24" max="24" width="15.88671875" customWidth="1"/>
+    <col min="25" max="25" width="13.33203125" customWidth="1"/>
+    <col min="26" max="26" width="13.21875" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" customWidth="1"/>
+    <col min="28" max="28" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:33" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+    </row>
+    <row r="3" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+    </row>
+    <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <f>'معلومات الطلاب'!A4</f>
+        <v>1002</v>
+      </c>
+      <c r="B4" t="str">
+        <f>'معلومات الطلاب'!B4</f>
+        <v>نورة خالد العتيبي</v>
+      </c>
+      <c r="C4" t="str">
+        <f>'معلومات الطلاب'!D4</f>
+        <v>الخامس</v>
+      </c>
+      <c r="D4">
+        <f>'معلومات الطلاب'!E4</f>
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <f>'معلومات الطلاب'!F4</f>
+        <v>رياضيات</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2">
+        <v>5</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>20</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="6">
+        <v>20</v>
+      </c>
+      <c r="T4" s="6">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6">
+        <v>0</v>
+      </c>
+      <c r="V4" s="6">
+        <v>40</v>
+      </c>
+      <c r="W4" s="7">
+        <v>40</v>
+      </c>
+      <c r="X4">
+        <f>F4+H4+J4+L4+N4+P4+R4+T4+V4</f>
+        <v>87</v>
+      </c>
+      <c r="Y4">
+        <f>G4+I4+K4+M4+O4+Q4+S4+U4+W4</f>
+        <v>100</v>
+      </c>
+      <c r="Z4">
+        <f>X4/Y4</f>
+        <v>0.87</v>
+      </c>
+      <c r="AA4" t="str">
+        <f>IF(Z4&gt;=0.9,"ممتاز",IF(Z4&gt;=0.8,"جيد جداً",IF(Z4&gt;=0.7,"جيد",IF(Z4&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v>جيد جداً</v>
+      </c>
+      <c r="AB4" t="str">
+        <f>IF(Z4&lt;0.6,"متعثر",IF(Z4&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
+        <v>لا يحتاج متابعة</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <f>'معلومات الطلاب'!A5</f>
+        <v>1003</v>
+      </c>
+      <c r="B5" t="str">
+        <f>'معلومات الطلاب'!B5</f>
+        <v>ريم عبد الله السبيعي</v>
+      </c>
+      <c r="C5" t="str">
+        <f>'معلومات الطلاب'!D5</f>
+        <v>الخامس</v>
+      </c>
+      <c r="D5">
+        <f>'معلومات الطلاب'!E5</f>
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <f>'معلومات الطلاب'!F5</f>
+        <v>رياضيات</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
+        <v>5</v>
+      </c>
+      <c r="L5" s="2">
+        <v>5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>20</v>
+      </c>
+      <c r="R5" s="5">
+        <v>15</v>
+      </c>
+      <c r="S5" s="6">
+        <v>20</v>
+      </c>
+      <c r="T5" s="6">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6">
+        <v>40</v>
+      </c>
+      <c r="W5" s="7">
+        <v>40</v>
+      </c>
+      <c r="X5">
+        <f t="shared" ref="X5:Y13" si="0">F5+H5+J5+L5+N5+P5+R5+T5+V5</f>
+        <v>86</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" ref="Z5:Z13" si="1">X5/Y5</f>
+        <v>0.86</v>
+      </c>
+      <c r="AA5" t="str">
+        <f t="shared" ref="AA5:AA13" si="2">IF(Z5&gt;=0.9,"ممتاز",IF(Z5&gt;=0.8,"جيد جداً",IF(Z5&gt;=0.7,"جيد",IF(Z5&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v>جيد جداً</v>
+      </c>
+      <c r="AB5" t="str">
+        <f t="shared" ref="AB5:AB13" si="3">IF(Z5&lt;0.6,"متعثر",IF(Z5&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
+        <v>لا يحتاج متابعة</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <f>'معلومات الطلاب'!A6</f>
+        <v>1004</v>
+      </c>
+      <c r="B6" t="str">
+        <f>'معلومات الطلاب'!B6</f>
+        <v>شهد فهد القحطاني</v>
+      </c>
+      <c r="C6" t="str">
+        <f>'معلومات الطلاب'!D6</f>
+        <v>الخامس</v>
+      </c>
+      <c r="D6">
+        <f>'معلومات الطلاب'!E6</f>
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <f>'معلومات الطلاب'!F6</f>
+        <v>رياضيات</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5</v>
+      </c>
+      <c r="L6" s="2">
+        <v>4</v>
+      </c>
+      <c r="M6" s="2">
+        <v>5</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>20</v>
+      </c>
+      <c r="R6" s="5">
+        <v>15</v>
+      </c>
+      <c r="S6" s="6">
+        <v>20</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6">
+        <v>40</v>
+      </c>
+      <c r="W6" s="7">
+        <v>40</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="1"/>
+        <v>0.88</v>
+      </c>
+      <c r="AA6" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد جداً</v>
+      </c>
+      <c r="AB6" t="str">
+        <f t="shared" si="3"/>
+        <v>لا يحتاج متابعة</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <f>'معلومات الطلاب'!A7</f>
+        <v>1005</v>
+      </c>
+      <c r="B7" t="str">
+        <f>'معلومات الطلاب'!B7</f>
+        <v>مريم علي الشهري</v>
+      </c>
+      <c r="C7" t="str">
+        <f>'معلومات الطلاب'!D7</f>
+        <v>الخامس</v>
+      </c>
+      <c r="D7">
+        <f>'معلومات الطلاب'!E7</f>
+        <v>2</v>
+      </c>
+      <c r="E7" t="str">
+        <f>'معلومات الطلاب'!F7</f>
+        <v>رياضيات</v>
+      </c>
+      <c r="F7" s="2">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>20</v>
+      </c>
+      <c r="R7" s="7">
+        <v>10</v>
+      </c>
+      <c r="S7" s="6">
+        <v>20</v>
+      </c>
+      <c r="T7" s="6">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6">
+        <v>40</v>
+      </c>
+      <c r="W7" s="7">
+        <v>40</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="1"/>
+        <v>0.71</v>
+      </c>
+      <c r="AA7" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB7" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <f>'معلومات الطلاب'!A8</f>
+        <v>1006</v>
+      </c>
+      <c r="B8" t="str">
+        <f>'معلومات الطلاب'!B8</f>
+        <v>أروى محمد الدوسري</v>
+      </c>
+      <c r="C8" t="str">
+        <f>'معلومات الطلاب'!D8</f>
+        <v>السادس</v>
+      </c>
+      <c r="D8">
+        <f>'معلومات الطلاب'!E8</f>
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <f>'معلومات الطلاب'!F8</f>
+        <v>علوم</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5</v>
+      </c>
+      <c r="L8" s="2">
+        <v>3</v>
+      </c>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>20</v>
+      </c>
+      <c r="R8" s="7">
+        <v>18</v>
+      </c>
+      <c r="S8" s="6">
+        <v>20</v>
+      </c>
+      <c r="T8" s="6">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6">
+        <v>40</v>
+      </c>
+      <c r="W8" s="7">
+        <v>40</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="1"/>
+        <v>0.79</v>
+      </c>
+      <c r="AA8" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB8" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <f>'معلومات الطلاب'!A9</f>
+        <v>1007</v>
+      </c>
+      <c r="B9" t="str">
+        <f>'معلومات الطلاب'!B9</f>
+        <v>لجين حمد العبد الله</v>
+      </c>
+      <c r="C9" t="str">
+        <f>'معلومات الطلاب'!D9</f>
+        <v>السادس</v>
+      </c>
+      <c r="D9">
+        <f>'معلومات الطلاب'!E9</f>
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <f>'معلومات الطلاب'!F9</f>
+        <v>علوم</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5</v>
+      </c>
+      <c r="L9" s="2">
+        <v>3</v>
+      </c>
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>20</v>
+      </c>
+      <c r="R9" s="7">
+        <v>5</v>
+      </c>
+      <c r="S9" s="6">
+        <v>20</v>
+      </c>
+      <c r="T9" s="6">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
+        <v>0</v>
+      </c>
+      <c r="V9" s="6">
+        <v>40</v>
+      </c>
+      <c r="W9" s="7">
+        <v>40</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="AA9" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB9" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <f>'معلومات الطلاب'!A10</f>
+        <v>1008</v>
+      </c>
+      <c r="B10" t="str">
+        <f>'معلومات الطلاب'!B10</f>
+        <v>جود سلطان العتيبي</v>
+      </c>
+      <c r="C10" t="str">
+        <f>'معلومات الطلاب'!D10</f>
+        <v>السادس</v>
+      </c>
+      <c r="D10">
+        <f>'معلومات الطلاب'!E10</f>
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <f>'معلومات الطلاب'!F10</f>
+        <v>علوم</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5</v>
+      </c>
+      <c r="L10" s="2">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2">
+        <v>5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>20</v>
+      </c>
+      <c r="R10" s="7">
+        <v>11</v>
+      </c>
+      <c r="S10" s="6">
+        <v>20</v>
+      </c>
+      <c r="T10" s="6">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6">
+        <v>40</v>
+      </c>
+      <c r="W10" s="7">
+        <v>40</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="1"/>
+        <v>0.77</v>
+      </c>
+      <c r="AA10" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB10" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <f>'معلومات الطلاب'!A11</f>
+        <v>1009</v>
+      </c>
+      <c r="B11" t="str">
+        <f>'معلومات الطلاب'!B11</f>
+        <v>حلا يوسف المطر</v>
+      </c>
+      <c r="C11" t="str">
+        <f>'معلومات الطلاب'!D11</f>
+        <v>السادس</v>
+      </c>
+      <c r="D11">
+        <f>'معلومات الطلاب'!E11</f>
+        <v>2</v>
+      </c>
+      <c r="E11" t="str">
+        <f>'معلومات الطلاب'!F11</f>
+        <v>علوم</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2">
+        <v>4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>5</v>
+      </c>
+      <c r="L11" s="2">
+        <v>3</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>20</v>
+      </c>
+      <c r="R11" s="7">
+        <v>20</v>
+      </c>
+      <c r="S11" s="6">
+        <v>20</v>
+      </c>
+      <c r="T11" s="6">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6">
+        <v>40</v>
+      </c>
+      <c r="W11" s="7">
+        <v>40</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="1"/>
+        <v>0.74</v>
+      </c>
+      <c r="AA11" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB11" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <f>'معلومات الطلاب'!A12</f>
+        <v>1010</v>
+      </c>
+      <c r="B12" t="str">
+        <f>'معلومات الطلاب'!B12</f>
+        <v>غادة إبراهيم الزهراني</v>
+      </c>
+      <c r="C12" t="str">
+        <f>'معلومات الطلاب'!D12</f>
+        <v>السادس</v>
+      </c>
+      <c r="D12">
+        <f>'معلومات الطلاب'!E12</f>
+        <v>2</v>
+      </c>
+      <c r="E12" t="str">
+        <f>'معلومات الطلاب'!F12</f>
+        <v>علوم</v>
+      </c>
+      <c r="F12" s="2">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2">
+        <v>3</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>20</v>
+      </c>
+      <c r="R12" s="7">
+        <v>13</v>
+      </c>
+      <c r="S12" s="6">
+        <v>20</v>
+      </c>
+      <c r="T12" s="6">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6">
+        <v>40</v>
+      </c>
+      <c r="W12" s="7">
+        <v>40</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="1"/>
+        <v>0.73</v>
+      </c>
+      <c r="AA12" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB12" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <f>'معلومات الطلاب'!A13</f>
+        <v>1011</v>
+      </c>
+      <c r="B13" t="str">
+        <f>'معلومات الطلاب'!B13</f>
+        <v>نوهان ثروت علي</v>
+      </c>
+      <c r="C13" t="str">
+        <f>'معلومات الطلاب'!D13</f>
+        <v>السادس</v>
+      </c>
+      <c r="D13">
+        <f>'معلومات الطلاب'!E13</f>
+        <v>2</v>
+      </c>
+      <c r="E13" t="str">
+        <f>'معلومات الطلاب'!F13</f>
+        <v>علوم</v>
+      </c>
+      <c r="F13" s="2">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2">
+        <v>5</v>
+      </c>
+      <c r="L13" s="2">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>20</v>
+      </c>
+      <c r="R13" s="7">
+        <v>15</v>
+      </c>
+      <c r="S13" s="6">
+        <v>20</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0</v>
+      </c>
+      <c r="V13" s="6">
+        <v>40</v>
+      </c>
+      <c r="W13" s="7">
+        <v>40</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="1"/>
+        <v>0.78</v>
+      </c>
+      <c r="AA13" t="str">
+        <f t="shared" si="2"/>
+        <v>جيد</v>
+      </c>
+      <c r="AB13" t="str">
+        <f t="shared" si="3"/>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f>'معلومات الطلاب'!A14</f>
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <f>'معلومات الطلاب'!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f>'معلومات الطلاب'!D14</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>'معلومات الطلاب'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>'معلومات الطلاب'!F14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f>'معلومات الطلاب'!A15</f>
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <f>'معلومات الطلاب'!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f>'معلومات الطلاب'!D15</f>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>'معلومات الطلاب'!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>'معلومات الطلاب'!F15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f>'معلومات الطلاب'!A16</f>
+        <v>0</v>
+      </c>
+      <c r="B16">
+        <f>'معلومات الطلاب'!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f>'معلومات الطلاب'!D16</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f>'معلومات الطلاب'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>'معلومات الطلاب'!F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f>'معلومات الطلاب'!A17</f>
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <f>'معلومات الطلاب'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <f>'معلومات الطلاب'!D17</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <f>'معلومات الطلاب'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>'معلومات الطلاب'!F17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f>'معلومات الطلاب'!A18</f>
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <f>'معلومات الطلاب'!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <f>'معلومات الطلاب'!D18</f>
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <f>'معلومات الطلاب'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f>'معلومات الطلاب'!F18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <f>'معلومات الطلاب'!A19</f>
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <f>'معلومات الطلاب'!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f>'معلومات الطلاب'!D19</f>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f>'معلومات الطلاب'!E19</f>
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f>'معلومات الطلاب'!F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f>'معلومات الطلاب'!A20</f>
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <f>'معلومات الطلاب'!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f>'معلومات الطلاب'!D20</f>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <f>'معلومات الطلاب'!E20</f>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f>'معلومات الطلاب'!F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f>'معلومات الطلاب'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="B21">
+        <f>'معلومات الطلاب'!B21</f>
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <f>'معلومات الطلاب'!D21</f>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f>'معلومات الطلاب'!E21</f>
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f>'معلومات الطلاب'!F21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f>'معلومات الطلاب'!A22</f>
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <f>'معلومات الطلاب'!B22</f>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <f>'معلومات الطلاب'!D22</f>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f>'معلومات الطلاب'!E22</f>
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>'معلومات الطلاب'!F22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f>'معلومات الطلاب'!A23</f>
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <f>'معلومات الطلاب'!B23</f>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <f>'معلومات الطلاب'!D23</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>'معلومات الطلاب'!E23</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>'معلومات الطلاب'!F23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f>'معلومات الطلاب'!A24</f>
+        <v>0</v>
+      </c>
+      <c r="B24">
+        <f>'معلومات الطلاب'!B24</f>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f>'معلومات الطلاب'!D24</f>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f>'معلومات الطلاب'!E24</f>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>'معلومات الطلاب'!F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f>'معلومات الطلاب'!A25</f>
+        <v>0</v>
+      </c>
+      <c r="B25">
+        <f>'معلومات الطلاب'!B25</f>
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <f>'معلومات الطلاب'!D25</f>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f>'معلومات الطلاب'!E25</f>
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f>'معلومات الطلاب'!F25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <f>'معلومات الطلاب'!A26</f>
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <f>'معلومات الطلاب'!B26</f>
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <f>'معلومات الطلاب'!D26</f>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>'معلومات الطلاب'!E26</f>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>'معلومات الطلاب'!F26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <f>'معلومات الطلاب'!A27</f>
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <f>'معلومات الطلاب'!B27</f>
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <f>'معلومات الطلاب'!D27</f>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f>'معلومات الطلاب'!E27</f>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f>'معلومات الطلاب'!F27</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+    </row>
+    <row r="28" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+    </row>
+    <row r="29" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+    </row>
+    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+    </row>
+    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+    </row>
+    <row r="32" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+    </row>
+    <row r="33" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+    </row>
+    <row r="34" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+    </row>
+    <row r="35" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+    </row>
+    <row r="36" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+    </row>
+    <row r="37" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:AB2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الطلاب" sheetId="1" r:id="rId1"/>
     <sheet name="درجات الفصل الأول" sheetId="2" r:id="rId2"/>
     <sheet name="درجات الفصل الثاني" sheetId="4" r:id="rId3"/>
+    <sheet name="الداشبورد" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
   <si>
     <t>رقم الطالبة</t>
   </si>
@@ -178,13 +179,25 @@
   </si>
   <si>
     <t>السجل الشامل لدرجات وحالة أداء الطالبات - الفصل الدراسي الثاني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد الطلاب الكلي </t>
+  </si>
+  <si>
+    <t>عدد الطلاب المتعثرين</t>
+  </si>
+  <si>
+    <t>عدد الطلاب (المتابعات)</t>
+  </si>
+  <si>
+    <t>متوسط النسبة المئوية العامة</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +236,13 @@
     <font>
       <sz val="20"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -311,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -334,10 +354,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1477,36 +1506,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
     </row>
     <row r="3" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -2559,313 +2588,8 @@
         <v>محتاج متابعة</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <f>'معلومات الطلاب'!A14</f>
-        <v>0</v>
-      </c>
-      <c r="B14">
-        <f>'معلومات الطلاب'!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <f>'معلومات الطلاب'!D14</f>
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <f>'معلومات الطلاب'!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f>'معلومات الطلاب'!F14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <f>'معلومات الطلاب'!A15</f>
-        <v>0</v>
-      </c>
-      <c r="B15">
-        <f>'معلومات الطلاب'!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <f>'معلومات الطلاب'!D15</f>
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <f>'معلومات الطلاب'!E15</f>
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f>'معلومات الطلاب'!F15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <f>'معلومات الطلاب'!A16</f>
-        <v>0</v>
-      </c>
-      <c r="B16">
-        <f>'معلومات الطلاب'!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <f>'معلومات الطلاب'!D16</f>
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <f>'معلومات الطلاب'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f>'معلومات الطلاب'!F16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <f>'معلومات الطلاب'!A17</f>
-        <v>0</v>
-      </c>
-      <c r="B17">
-        <f>'معلومات الطلاب'!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <f>'معلومات الطلاب'!D17</f>
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <f>'معلومات الطلاب'!E17</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f>'معلومات الطلاب'!F17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <f>'معلومات الطلاب'!A18</f>
-        <v>0</v>
-      </c>
-      <c r="B18">
-        <f>'معلومات الطلاب'!B18</f>
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <f>'معلومات الطلاب'!D18</f>
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <f>'معلومات الطلاب'!E18</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <f>'معلومات الطلاب'!F18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <f>'معلومات الطلاب'!A19</f>
-        <v>0</v>
-      </c>
-      <c r="B19">
-        <f>'معلومات الطلاب'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <f>'معلومات الطلاب'!D19</f>
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <f>'معلومات الطلاب'!E19</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <f>'معلومات الطلاب'!F19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <f>'معلومات الطلاب'!A20</f>
-        <v>0</v>
-      </c>
-      <c r="B20">
-        <f>'معلومات الطلاب'!B20</f>
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <f>'معلومات الطلاب'!D20</f>
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <f>'معلومات الطلاب'!E20</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <f>'معلومات الطلاب'!F20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <f>'معلومات الطلاب'!A21</f>
-        <v>0</v>
-      </c>
-      <c r="B21">
-        <f>'معلومات الطلاب'!B21</f>
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <f>'معلومات الطلاب'!D21</f>
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <f>'معلومات الطلاب'!E21</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <f>'معلومات الطلاب'!F21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <f>'معلومات الطلاب'!A22</f>
-        <v>0</v>
-      </c>
-      <c r="B22">
-        <f>'معلومات الطلاب'!B22</f>
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <f>'معلومات الطلاب'!D22</f>
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <f>'معلومات الطلاب'!E22</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <f>'معلومات الطلاب'!F22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <f>'معلومات الطلاب'!A23</f>
-        <v>0</v>
-      </c>
-      <c r="B23">
-        <f>'معلومات الطلاب'!B23</f>
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <f>'معلومات الطلاب'!D23</f>
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <f>'معلومات الطلاب'!E23</f>
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <f>'معلومات الطلاب'!F23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <f>'معلومات الطلاب'!A24</f>
-        <v>0</v>
-      </c>
-      <c r="B24">
-        <f>'معلومات الطلاب'!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <f>'معلومات الطلاب'!D24</f>
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <f>'معلومات الطلاب'!E24</f>
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <f>'معلومات الطلاب'!F24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <f>'معلومات الطلاب'!A25</f>
-        <v>0</v>
-      </c>
-      <c r="B25">
-        <f>'معلومات الطلاب'!B25</f>
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <f>'معلومات الطلاب'!D25</f>
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <f>'معلومات الطلاب'!E25</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <f>'معلومات الطلاب'!F25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <f>'معلومات الطلاب'!A26</f>
-        <v>0</v>
-      </c>
-      <c r="B26">
-        <f>'معلومات الطلاب'!B26</f>
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <f>'معلومات الطلاب'!D26</f>
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <f>'معلومات الطلاب'!E26</f>
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <f>'معلومات الطلاب'!F26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <f>'معلومات الطلاب'!A27</f>
-        <v>0</v>
-      </c>
-      <c r="B27">
-        <f>'معلومات الطلاب'!B27</f>
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <f>'معلومات الطلاب'!D27</f>
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <f>'معلومات الطلاب'!E27</f>
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <f>'معلومات الطلاب'!F27</f>
-        <v>0</v>
-      </c>
+    <row r="26" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2877,7 +2601,7 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -2889,7 +2613,7 @@
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
     </row>
-    <row r="29" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -2901,7 +2625,7 @@
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
     </row>
-    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -2913,7 +2637,7 @@
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
     </row>
-    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -2925,7 +2649,7 @@
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
     </row>
-    <row r="32" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -3038,36 +2762,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
     </row>
     <row r="3" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -4568,4 +4292,128 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="J3:U8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J4" s="11">
+        <f>AVERAGE('درجات الفصل الأول'!Z:Z, 'درجات الفصل الثاني'!Z:Z)</f>
+        <v>0.73349999999999993</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11">
+        <f>COUNTIF('درجات الفصل الأول'!AB:AB, "محتاج متابعة") + COUNTIF('درجات الفصل الثاني'!AB:AB, "محتاج متابعة")</f>
+        <v>14</v>
+      </c>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11">
+        <f>COUNTIF('درجات الفصل الأول'!AB:AB, "متعثر") + COUNTIF('درجات الفصل الثاني'!AB:AB, "متعثر")</f>
+        <v>2</v>
+      </c>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11">
+        <f>COUNT('درجات الفصل الأول'!A:A)</f>
+        <v>10</v>
+      </c>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+    </row>
+    <row r="5" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+    </row>
+    <row r="6" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+    </row>
+    <row r="7" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+    </row>
+    <row r="8" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="J4:L8"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="S4:U8"/>
+    <mergeCell ref="P4:R8"/>
+    <mergeCell ref="M4:O8"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="M3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="63">
   <si>
     <t>رقم الطالبة</t>
   </si>
@@ -191,13 +191,28 @@
   </si>
   <si>
     <t>متوسط النسبة المئوية العامة</t>
+  </si>
+  <si>
+    <t>ممتاز</t>
+  </si>
+  <si>
+    <t>جيد جداً</t>
+  </si>
+  <si>
+    <t>جيد</t>
+  </si>
+  <si>
+    <t>مقبول</t>
+  </si>
+  <si>
+    <t>ضعيف</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +258,13 @@
     <font>
       <sz val="48"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -341,9 +363,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -357,6 +376,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -366,8 +388,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -376,44 +404,16 @@
   <dxfs count="17">
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4C7C5"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="medium">
           <color rgb="FFC4C7C5"/>
         </top>
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
+      <border outline="0">
+        <bottom style="medium">
           <color rgb="FFC4C7C5"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFC4C7C5"/>
-        </right>
-        <top/>
-        <bottom/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -446,16 +446,44 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFC4C7C5"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="medium">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
           <color rgb="FFC4C7C5"/>
-        </top>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -766,6 +794,178 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>الداشبورد!$B$4:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>ممتاز</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>جيد جداً</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>جيد</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>مقبول</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ضعيف</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>الداشبورد!$C$4:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="141396992"/>
+        <c:axId val="203290112"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="141396992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="203290112"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="203290112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="141396992"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="مخطط 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:G16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A2:G16"/>
@@ -783,7 +983,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="الجدول1" displayName="الجدول1" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="الجدول1" displayName="الجدول1" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A3:AB411"/>
   <tableColumns count="28">
     <tableColumn id="1" name="رقم"/>
@@ -820,7 +1020,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="الجدول13" displayName="الجدول13" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="الجدول13" displayName="الجدول13" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A3:AB411"/>
   <tableColumns count="28">
     <tableColumn id="1" name="رقم"/>
@@ -1156,15 +1356,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -1682,25 +1882,25 @@
       <c r="P4" s="2">
         <v>19</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>20</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>18</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="5">
         <v>20</v>
       </c>
-      <c r="T4" s="6">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
         <v>35</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="6">
         <v>40</v>
       </c>
       <c r="X4">
@@ -1778,25 +1978,25 @@
       <c r="P5" s="2">
         <v>15</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
         <v>20</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R5" s="4">
         <v>13</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="5">
         <v>20</v>
       </c>
-      <c r="T5" s="6">
-        <v>0</v>
-      </c>
-      <c r="U5" s="6">
-        <v>0</v>
-      </c>
-      <c r="V5" s="6">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5">
         <v>33</v>
       </c>
-      <c r="W5" s="7">
+      <c r="W5" s="6">
         <v>40</v>
       </c>
       <c r="X5">
@@ -1874,25 +2074,25 @@
       <c r="P6" s="2">
         <v>8</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="4">
         <v>20</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="4">
         <v>15</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <v>20</v>
       </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
         <v>15</v>
       </c>
-      <c r="W6" s="7">
+      <c r="W6" s="6">
         <v>40</v>
       </c>
       <c r="X6">
@@ -1970,25 +2170,25 @@
       <c r="P7" s="2">
         <v>4</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="4">
         <v>20</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <v>10</v>
       </c>
-      <c r="S7" s="6">
+      <c r="S7" s="5">
         <v>20</v>
       </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="7">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6">
         <v>33</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="6">
         <v>40</v>
       </c>
       <c r="X7">
@@ -2066,25 +2266,25 @@
       <c r="P8" s="2">
         <v>13</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="4">
         <v>20</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="6">
         <v>18</v>
       </c>
-      <c r="S8" s="6">
+      <c r="S8" s="5">
         <v>20</v>
       </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="7">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6">
         <v>33</v>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="6">
         <v>40</v>
       </c>
       <c r="X8">
@@ -2162,25 +2362,25 @@
       <c r="P9" s="2">
         <v>18</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="4">
         <v>20</v>
       </c>
-      <c r="R9" s="7">
-        <v>5</v>
-      </c>
-      <c r="S9" s="6">
+      <c r="R9" s="6">
+        <v>5</v>
+      </c>
+      <c r="S9" s="5">
         <v>20</v>
       </c>
-      <c r="T9" s="6">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="6">
         <v>33</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="6">
         <v>40</v>
       </c>
       <c r="X9">
@@ -2258,25 +2458,25 @@
       <c r="P10" s="2">
         <v>16</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="4">
         <v>20</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="6">
         <v>11</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="5">
         <v>20</v>
       </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>0</v>
-      </c>
-      <c r="V10" s="7">
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6">
         <v>33</v>
       </c>
-      <c r="W10" s="7">
+      <c r="W10" s="6">
         <v>40</v>
       </c>
       <c r="X10">
@@ -2354,25 +2554,25 @@
       <c r="P11" s="2">
         <v>3</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q11" s="4">
         <v>20</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <v>20</v>
       </c>
-      <c r="S11" s="6">
+      <c r="S11" s="5">
         <v>20</v>
       </c>
-      <c r="T11" s="6">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6">
-        <v>0</v>
-      </c>
-      <c r="V11" s="7">
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6">
         <v>33</v>
       </c>
-      <c r="W11" s="7">
+      <c r="W11" s="6">
         <v>40</v>
       </c>
       <c r="X11">
@@ -2450,25 +2650,25 @@
       <c r="P12" s="2">
         <v>6</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="4">
         <v>20</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="6">
         <v>13</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="5">
         <v>20</v>
       </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
-        <v>0</v>
-      </c>
-      <c r="V12" s="7">
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6">
         <v>33</v>
       </c>
-      <c r="W12" s="7">
+      <c r="W12" s="6">
         <v>40</v>
       </c>
       <c r="X12">
@@ -2546,25 +2746,25 @@
       <c r="P13" s="2">
         <v>11</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="Q13" s="4">
         <v>20</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="6">
         <v>15</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="5">
         <v>20</v>
       </c>
-      <c r="T13" s="6">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6">
-        <v>0</v>
-      </c>
-      <c r="V13" s="7">
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="6">
         <v>33</v>
       </c>
-      <c r="W13" s="7">
+      <c r="W13" s="6">
         <v>40</v>
       </c>
       <c r="X13">
@@ -2938,25 +3138,25 @@
       <c r="P4" s="2">
         <v>19</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>20</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>18</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="5">
         <v>20</v>
       </c>
-      <c r="T4" s="6">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6">
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
         <v>40</v>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="6">
         <v>40</v>
       </c>
       <c r="X4">
@@ -3034,25 +3234,25 @@
       <c r="P5" s="2">
         <v>15</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="4">
         <v>20</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R5" s="4">
         <v>15</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="5">
         <v>20</v>
       </c>
-      <c r="T5" s="6">
-        <v>0</v>
-      </c>
-      <c r="U5" s="6">
-        <v>0</v>
-      </c>
-      <c r="V5" s="6">
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5">
         <v>40</v>
       </c>
-      <c r="W5" s="7">
+      <c r="W5" s="6">
         <v>40</v>
       </c>
       <c r="X5">
@@ -3130,25 +3330,25 @@
       <c r="P6" s="2">
         <v>16</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="4">
         <v>20</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="4">
         <v>15</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <v>20</v>
       </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>0</v>
-      </c>
-      <c r="V6" s="6">
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
         <v>40</v>
       </c>
-      <c r="W6" s="7">
+      <c r="W6" s="6">
         <v>40</v>
       </c>
       <c r="X6">
@@ -3226,25 +3426,25 @@
       <c r="P7" s="2">
         <v>4</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="4">
         <v>20</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <v>10</v>
       </c>
-      <c r="S7" s="6">
+      <c r="S7" s="5">
         <v>20</v>
       </c>
-      <c r="T7" s="6">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6">
-        <v>0</v>
-      </c>
-      <c r="V7" s="6">
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5">
         <v>40</v>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="6">
         <v>40</v>
       </c>
       <c r="X7">
@@ -3322,25 +3522,25 @@
       <c r="P8" s="2">
         <v>13</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="4">
         <v>20</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="6">
         <v>18</v>
       </c>
-      <c r="S8" s="6">
+      <c r="S8" s="5">
         <v>20</v>
       </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
         <v>40</v>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="6">
         <v>40</v>
       </c>
       <c r="X8">
@@ -3418,25 +3618,25 @@
       <c r="P9" s="2">
         <v>18</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="4">
         <v>20</v>
       </c>
-      <c r="R9" s="7">
-        <v>5</v>
-      </c>
-      <c r="S9" s="6">
+      <c r="R9" s="6">
+        <v>5</v>
+      </c>
+      <c r="S9" s="5">
         <v>20</v>
       </c>
-      <c r="T9" s="6">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6">
-        <v>0</v>
-      </c>
-      <c r="V9" s="6">
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5">
         <v>40</v>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="6">
         <v>40</v>
       </c>
       <c r="X9">
@@ -3514,25 +3714,25 @@
       <c r="P10" s="2">
         <v>16</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="4">
         <v>20</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="6">
         <v>11</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="5">
         <v>20</v>
       </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>0</v>
-      </c>
-      <c r="V10" s="6">
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
         <v>40</v>
       </c>
-      <c r="W10" s="7">
+      <c r="W10" s="6">
         <v>40</v>
       </c>
       <c r="X10">
@@ -3610,25 +3810,25 @@
       <c r="P11" s="2">
         <v>3</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q11" s="4">
         <v>20</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <v>20</v>
       </c>
-      <c r="S11" s="6">
+      <c r="S11" s="5">
         <v>20</v>
       </c>
-      <c r="T11" s="6">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6">
-        <v>0</v>
-      </c>
-      <c r="V11" s="6">
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
         <v>40</v>
       </c>
-      <c r="W11" s="7">
+      <c r="W11" s="6">
         <v>40</v>
       </c>
       <c r="X11">
@@ -3706,25 +3906,25 @@
       <c r="P12" s="2">
         <v>6</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="4">
         <v>20</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="6">
         <v>13</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="5">
         <v>20</v>
       </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6">
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
         <v>40</v>
       </c>
-      <c r="W12" s="7">
+      <c r="W12" s="6">
         <v>40</v>
       </c>
       <c r="X12">
@@ -3802,25 +4002,25 @@
       <c r="P13" s="2">
         <v>11</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="Q13" s="4">
         <v>20</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="6">
         <v>15</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="5">
         <v>20</v>
       </c>
-      <c r="T13" s="6">
-        <v>0</v>
-      </c>
-      <c r="U13" s="6">
-        <v>0</v>
-      </c>
-      <c r="V13" s="6">
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
         <v>40</v>
       </c>
-      <c r="W13" s="7">
+      <c r="W13" s="6">
         <v>40</v>
       </c>
       <c r="X13">
@@ -4296,32 +4496,43 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="J3:U8"/>
+  <dimension ref="B3:W10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="9" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="10:21" x14ac:dyDescent="0.3">
-      <c r="J3" s="8" t="s">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="J3" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="12" t="s">
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="8" t="s">
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8" t="s">
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-    </row>
-    <row r="4" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B4" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4">
+        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "ممتاز") + COUNTIF('درجات الفصل الثاني'!AA:AA, "ممتاز")</f>
+        <v>0</v>
+      </c>
       <c r="J4" s="11">
         <f>AVERAGE('درجات الفصل الأول'!Z:Z, 'درجات الفصل الثاني'!Z:Z)</f>
         <v>0.73349999999999993</v>
@@ -4346,8 +4557,17 @@
       </c>
       <c r="T4" s="11"/>
       <c r="U4" s="11"/>
-    </row>
-    <row r="5" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5">
+        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "جيد جداً") + COUNTIF('درجات الفصل الثاني'!AA:AA, "جيد جداً")</f>
+        <v>4</v>
+      </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
@@ -4360,8 +4580,17 @@
       <c r="S5" s="11"/>
       <c r="T5" s="11"/>
       <c r="U5" s="11"/>
-    </row>
-    <row r="6" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B6" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "جيد") + COUNTIF('درجات الفصل الثاني'!AA:AA, "جيد")</f>
+        <v>10</v>
+      </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -4374,8 +4603,17 @@
       <c r="S6" s="11"/>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
-    </row>
-    <row r="7" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "مقبول") + COUNTIF('درجات الفصل الثاني'!AA:AA, "مقبول")</f>
+        <v>4</v>
+      </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -4388,8 +4626,17 @@
       <c r="S7" s="11"/>
       <c r="T7" s="11"/>
       <c r="U7" s="11"/>
-    </row>
-    <row r="8" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "ضعيف") + COUNTIF('درجات الفصل الثاني'!AA:AA, "ضعيف")</f>
+        <v>2</v>
+      </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -4402,9 +4649,20 @@
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="V9:W10"/>
     <mergeCell ref="J4:L8"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="S4:U8"/>
@@ -4415,5 +4673,19 @@
     <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>'درجات الفصل الأول'!B:B</xm:f>
+          </x14:formula1>
+          <xm:sqref>V9:W10</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -4,20 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الطلاب" sheetId="1" r:id="rId1"/>
     <sheet name="درجات الفصل الأول" sheetId="2" r:id="rId2"/>
     <sheet name="درجات الفصل الثاني" sheetId="4" r:id="rId3"/>
-    <sheet name="الداشبورد" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
   <si>
     <t>رقم الطالبة</t>
   </si>
@@ -179,40 +178,13 @@
   </si>
   <si>
     <t>السجل الشامل لدرجات وحالة أداء الطالبات - الفصل الدراسي الثاني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عدد الطلاب الكلي </t>
-  </si>
-  <si>
-    <t>عدد الطلاب المتعثرين</t>
-  </si>
-  <si>
-    <t>عدد الطلاب (المتابعات)</t>
-  </si>
-  <si>
-    <t>متوسط النسبة المئوية العامة</t>
-  </si>
-  <si>
-    <t>ممتاز</t>
-  </si>
-  <si>
-    <t>جيد جداً</t>
-  </si>
-  <si>
-    <t>جيد</t>
-  </si>
-  <si>
-    <t>مقبول</t>
-  </si>
-  <si>
-    <t>ضعيف</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,20 +223,6 @@
     <font>
       <sz val="20"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -353,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -373,9 +331,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -384,18 +339,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -794,178 +737,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>الداشبورد!$B$4:$B$8</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>ممتاز</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>جيد جداً</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>جيد</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>مقبول</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>ضعيف</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>الداشبورد!$C$4:$C$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="141396992"/>
-        <c:axId val="203290112"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="141396992"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="203290112"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="203290112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="141396992"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="مخطط 3"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:G16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A2:G16"/>
@@ -1356,15 +1127,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -1706,36 +1477,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
     </row>
     <row r="3" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -2962,36 +2733,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
     </row>
     <row r="3" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
@@ -4492,200 +4263,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:W10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="8" max="9" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="J3" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-    </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B4" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4">
-        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "ممتاز") + COUNTIF('درجات الفصل الثاني'!AA:AA, "ممتاز")</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="11">
-        <f>AVERAGE('درجات الفصل الأول'!Z:Z, 'درجات الفصل الثاني'!Z:Z)</f>
-        <v>0.73349999999999993</v>
-      </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11">
-        <f>COUNTIF('درجات الفصل الأول'!AB:AB, "محتاج متابعة") + COUNTIF('درجات الفصل الثاني'!AB:AB, "محتاج متابعة")</f>
-        <v>14</v>
-      </c>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11">
-        <f>COUNTIF('درجات الفصل الأول'!AB:AB, "متعثر") + COUNTIF('درجات الفصل الثاني'!AB:AB, "متعثر")</f>
-        <v>2</v>
-      </c>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11">
-        <f>COUNT('درجات الفصل الأول'!A:A)</f>
-        <v>10</v>
-      </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-    </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5">
-        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "جيد جداً") + COUNTIF('درجات الفصل الثاني'!AA:AA, "جيد جداً")</f>
-        <v>4</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-    </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "جيد") + COUNTIF('درجات الفصل الثاني'!AA:AA, "جيد")</f>
-        <v>10</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "مقبول") + COUNTIF('درجات الفصل الثاني'!AA:AA, "مقبول")</f>
-        <v>4</v>
-      </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-    </row>
-    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
-        <f>COUNTIF('درجات الفصل الأول'!AA:AA, "ضعيف") + COUNTIF('درجات الفصل الثاني'!AA:AA, "ضعيف")</f>
-        <v>2</v>
-      </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-    </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-    </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="J4:L8"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="S4:U8"/>
-    <mergeCell ref="P4:R8"/>
-    <mergeCell ref="M4:O8"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="M3:O3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'درجات الفصل الأول'!B:B</xm:f>
-          </x14:formula1>
-          <xm:sqref>V9:W10</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الطلاب" sheetId="1" r:id="rId1"/>
-    <sheet name="درجات الفصل الأول" sheetId="2" r:id="rId2"/>
+    <sheet name="درجات الفصل الاول" sheetId="2" r:id="rId2"/>
     <sheet name="درجات الفصل الثاني" sheetId="4" r:id="rId3"/>
+    <sheet name="ورقة1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="57">
   <si>
     <t>رقم الطالبة</t>
   </si>
@@ -178,6 +179,15 @@
   </si>
   <si>
     <t>السجل الشامل لدرجات وحالة أداء الطالبات - الفصل الدراسي الثاني</t>
+  </si>
+  <si>
+    <t>سلمى محمد على يوسف</t>
+  </si>
+  <si>
+    <t>2027 - 2026</t>
+  </si>
+  <si>
+    <t>لغتي</t>
   </si>
 </sst>
 </file>
@@ -1414,11 +1424,27 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="A14">
+        <v>1012</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="2"/>
@@ -2559,6 +2585,102 @@
         <v>محتاج متابعة</v>
       </c>
     </row>
+    <row r="14" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <f>'معلومات الطلاب'!A14</f>
+        <v>1012</v>
+      </c>
+      <c r="B14" t="str">
+        <f>'معلومات الطلاب'!B14</f>
+        <v>سلمى محمد على يوسف</v>
+      </c>
+      <c r="C14" t="str">
+        <f>'معلومات الطلاب'!D14</f>
+        <v>السادس</v>
+      </c>
+      <c r="D14">
+        <f>'معلومات الطلاب'!E14</f>
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
+        <f>'معلومات الطلاب'!F14</f>
+        <v>لغتي</v>
+      </c>
+      <c r="F14" s="2">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2">
+        <v>3</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>20</v>
+      </c>
+      <c r="R14" s="6">
+        <v>15</v>
+      </c>
+      <c r="S14" s="5">
+        <v>20</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="6">
+        <v>33</v>
+      </c>
+      <c r="W14" s="6">
+        <v>40</v>
+      </c>
+      <c r="X14">
+        <f t="shared" ref="X14" si="5">F14+H14+J14+L14+N14+P14+R14+T14+V14</f>
+        <v>72</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" ref="Y14" si="6">G14+I14+K14+M14+O14+Q14+S14+U14+W14</f>
+        <v>100</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" ref="Z14" si="7">X14/Y14</f>
+        <v>0.72</v>
+      </c>
+      <c r="AA14" t="str">
+        <f t="shared" ref="AA14" si="8">IF(Z14&gt;=0.9,"ممتاز",IF(Z14&gt;=0.8,"جيد جداً",IF(Z14&gt;=0.7,"جيد",IF(Z14&gt;=0.6,"مقبول","ضعيف"))))</f>
+        <v>جيد</v>
+      </c>
+      <c r="AB14" t="str">
+        <f t="shared" ref="AB14" si="9">IF(Z14&lt;0.6,"متعثر",IF(Z14&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
+        <v>محتاج متابعة</v>
+      </c>
+    </row>
     <row r="26" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N27" s="1"/>
@@ -3818,23 +3940,23 @@
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>'معلومات الطلاب'!A14</f>
-        <v>0</v>
-      </c>
-      <c r="B14">
+        <v>1012</v>
+      </c>
+      <c r="B14" t="str">
         <f>'معلومات الطلاب'!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C14">
+        <v>سلمى محمد على يوسف</v>
+      </c>
+      <c r="C14" t="str">
         <f>'معلومات الطلاب'!D14</f>
-        <v>0</v>
+        <v>السادس</v>
       </c>
       <c r="D14">
         <f>'معلومات الطلاب'!E14</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
         <f>'معلومات الطلاب'!F14</f>
-        <v>0</v>
+        <v>لغتي</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -4263,4 +4385,13 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الطلاب" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,9 @@
     <sheet name="درجات الفصل الثاني" sheetId="4" r:id="rId3"/>
     <sheet name="ورقة1" sheetId="5" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
@@ -747,6 +750,19 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="الفصل الدراسي الاول"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:G16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A2:G16"/>
@@ -1627,12 +1643,12 @@
     </row>
     <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
-        <f>'معلومات الطلاب'!A4</f>
-        <v>1002</v>
+        <f>'معلومات الطلاب'!A3</f>
+        <v>1001</v>
       </c>
       <c r="B4" t="str">
-        <f>'معلومات الطلاب'!B4</f>
-        <v>نورة خالد العتيبي</v>
+        <f>'معلومات الطلاب'!B3</f>
+        <v>سارة أحمد المحمد</v>
       </c>
       <c r="C4" t="str">
         <f>'معلومات الطلاب'!D4</f>
@@ -1723,12 +1739,12 @@
     </row>
     <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
-        <f>'معلومات الطلاب'!A5</f>
-        <v>1003</v>
+        <f>'معلومات الطلاب'!A4</f>
+        <v>1002</v>
       </c>
       <c r="B5" t="str">
-        <f>'معلومات الطلاب'!B5</f>
-        <v>ريم عبد الله السبيعي</v>
+        <f>'معلومات الطلاب'!B4</f>
+        <v>نورة خالد العتيبي</v>
       </c>
       <c r="C5" t="str">
         <f>'معلومات الطلاب'!D5</f>
@@ -1819,12 +1835,12 @@
     </row>
     <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
-        <f>'معلومات الطلاب'!A6</f>
-        <v>1004</v>
+        <f>'معلومات الطلاب'!A5</f>
+        <v>1003</v>
       </c>
       <c r="B6" t="str">
-        <f>'معلومات الطلاب'!B6</f>
-        <v>شهد فهد القحطاني</v>
+        <f>'معلومات الطلاب'!B5</f>
+        <v>ريم عبد الله السبيعي</v>
       </c>
       <c r="C6" t="str">
         <f>'معلومات الطلاب'!D6</f>
@@ -1915,12 +1931,12 @@
     </row>
     <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
-        <f>'معلومات الطلاب'!A7</f>
-        <v>1005</v>
+        <f>'معلومات الطلاب'!A6</f>
+        <v>1004</v>
       </c>
       <c r="B7" t="str">
-        <f>'معلومات الطلاب'!B7</f>
-        <v>مريم علي الشهري</v>
+        <f>'معلومات الطلاب'!B6</f>
+        <v>شهد فهد القحطاني</v>
       </c>
       <c r="C7" t="str">
         <f>'معلومات الطلاب'!D7</f>
@@ -2011,12 +2027,12 @@
     </row>
     <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8">
-        <f>'معلومات الطلاب'!A8</f>
-        <v>1006</v>
+        <f>'معلومات الطلاب'!A7</f>
+        <v>1005</v>
       </c>
       <c r="B8" t="str">
-        <f>'معلومات الطلاب'!B8</f>
-        <v>أروى محمد الدوسري</v>
+        <f>'معلومات الطلاب'!B7</f>
+        <v>مريم علي الشهري</v>
       </c>
       <c r="C8" t="str">
         <f>'معلومات الطلاب'!D8</f>
@@ -2107,12 +2123,12 @@
     </row>
     <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
-        <f>'معلومات الطلاب'!A9</f>
-        <v>1007</v>
+        <f>'معلومات الطلاب'!A8</f>
+        <v>1006</v>
       </c>
       <c r="B9" t="str">
-        <f>'معلومات الطلاب'!B9</f>
-        <v>لجين حمد العبد الله</v>
+        <f>'معلومات الطلاب'!B8</f>
+        <v>أروى محمد الدوسري</v>
       </c>
       <c r="C9" t="str">
         <f>'معلومات الطلاب'!D9</f>
@@ -2203,12 +2219,12 @@
     </row>
     <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10">
-        <f>'معلومات الطلاب'!A10</f>
-        <v>1008</v>
+        <f>'معلومات الطلاب'!A9</f>
+        <v>1007</v>
       </c>
       <c r="B10" t="str">
-        <f>'معلومات الطلاب'!B10</f>
-        <v>جود سلطان العتيبي</v>
+        <f>'معلومات الطلاب'!B9</f>
+        <v>لجين حمد العبد الله</v>
       </c>
       <c r="C10" t="str">
         <f>'معلومات الطلاب'!D10</f>
@@ -2299,12 +2315,12 @@
     </row>
     <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11">
-        <f>'معلومات الطلاب'!A11</f>
-        <v>1009</v>
+        <f>'معلومات الطلاب'!A10</f>
+        <v>1008</v>
       </c>
       <c r="B11" t="str">
-        <f>'معلومات الطلاب'!B11</f>
-        <v>حلا يوسف المطر</v>
+        <f>'معلومات الطلاب'!B10</f>
+        <v>جود سلطان العتيبي</v>
       </c>
       <c r="C11" t="str">
         <f>'معلومات الطلاب'!D11</f>
@@ -2395,12 +2411,12 @@
     </row>
     <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
-        <f>'معلومات الطلاب'!A12</f>
-        <v>1010</v>
+        <f>'معلومات الطلاب'!A11</f>
+        <v>1009</v>
       </c>
       <c r="B12" t="str">
-        <f>'معلومات الطلاب'!B12</f>
-        <v>غادة إبراهيم الزهراني</v>
+        <f>'معلومات الطلاب'!B11</f>
+        <v>حلا يوسف المطر</v>
       </c>
       <c r="C12" t="str">
         <f>'معلومات الطلاب'!D12</f>
@@ -2491,12 +2507,12 @@
     </row>
     <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13">
-        <f>'معلومات الطلاب'!A13</f>
-        <v>1011</v>
+        <f>'معلومات الطلاب'!A12</f>
+        <v>1010</v>
       </c>
       <c r="B13" t="str">
-        <f>'معلومات الطلاب'!B13</f>
-        <v>نوهان ثروت علي</v>
+        <f>'معلومات الطلاب'!B12</f>
+        <v>غادة إبراهيم الزهراني</v>
       </c>
       <c r="C13" t="str">
         <f>'معلومات الطلاب'!D13</f>
@@ -2587,12 +2603,12 @@
     </row>
     <row r="14" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
-        <f>'معلومات الطلاب'!A14</f>
-        <v>1012</v>
+        <f>'معلومات الطلاب'!A13</f>
+        <v>1011</v>
       </c>
       <c r="B14" t="str">
-        <f>'معلومات الطلاب'!B14</f>
-        <v>سلمى محمد على يوسف</v>
+        <f>'معلومات الطلاب'!B13</f>
+        <v>نوهان ثروت علي</v>
       </c>
       <c r="C14" t="str">
         <f>'معلومات الطلاب'!D14</f>
@@ -2679,6 +2695,16 @@
       <c r="AB14" t="str">
         <f t="shared" ref="AB14" si="9">IF(Z14&lt;0.6,"متعثر",IF(Z14&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
         <v>محتاج متابعة</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f>'معلومات الطلاب'!A14</f>
+        <v>1012</v>
+      </c>
+      <c r="B15" t="str">
+        <f>'معلومات الطلاب'!B14</f>
+        <v>سلمى محمد على يوسف</v>
       </c>
     </row>
     <row r="26" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -2979,23 +3005,23 @@
     </row>
     <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
-        <f>'معلومات الطلاب'!A4</f>
-        <v>1002</v>
+        <f>'معلومات الطلاب'!A3</f>
+        <v>1001</v>
       </c>
       <c r="B4" t="str">
-        <f>'معلومات الطلاب'!B4</f>
-        <v>نورة خالد العتيبي</v>
+        <f>'معلومات الطلاب'!B3</f>
+        <v>سارة أحمد المحمد</v>
       </c>
       <c r="C4" t="str">
-        <f>'معلومات الطلاب'!D4</f>
+        <f>'معلومات الطلاب'!D3</f>
         <v>الخامس</v>
       </c>
       <c r="D4">
-        <f>'معلومات الطلاب'!E4</f>
+        <f>'معلومات الطلاب'!E3</f>
         <v>1</v>
       </c>
       <c r="E4" t="str">
-        <f>'معلومات الطلاب'!F4</f>
+        <f>'معلومات الطلاب'!F3</f>
         <v>رياضيات</v>
       </c>
       <c r="F4" s="2">
@@ -3075,23 +3101,23 @@
     </row>
     <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
-        <f>'معلومات الطلاب'!A5</f>
-        <v>1003</v>
+        <f>'معلومات الطلاب'!A4</f>
+        <v>1002</v>
       </c>
       <c r="B5" t="str">
-        <f>'معلومات الطلاب'!B5</f>
-        <v>ريم عبد الله السبيعي</v>
+        <f>'معلومات الطلاب'!B4</f>
+        <v>نورة خالد العتيبي</v>
       </c>
       <c r="C5" t="str">
-        <f>'معلومات الطلاب'!D5</f>
+        <f>'معلومات الطلاب'!D4</f>
         <v>الخامس</v>
       </c>
       <c r="D5">
-        <f>'معلومات الطلاب'!E5</f>
+        <f>'معلومات الطلاب'!E4</f>
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <f>'معلومات الطلاب'!F5</f>
+        <f>'معلومات الطلاب'!F4</f>
         <v>رياضيات</v>
       </c>
       <c r="F5" s="2">
@@ -3171,23 +3197,23 @@
     </row>
     <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
-        <f>'معلومات الطلاب'!A6</f>
-        <v>1004</v>
+        <f>'معلومات الطلاب'!A5</f>
+        <v>1003</v>
       </c>
       <c r="B6" t="str">
-        <f>'معلومات الطلاب'!B6</f>
-        <v>شهد فهد القحطاني</v>
+        <f>'معلومات الطلاب'!B5</f>
+        <v>ريم عبد الله السبيعي</v>
       </c>
       <c r="C6" t="str">
-        <f>'معلومات الطلاب'!D6</f>
+        <f>'معلومات الطلاب'!D5</f>
         <v>الخامس</v>
       </c>
       <c r="D6">
-        <f>'معلومات الطلاب'!E6</f>
-        <v>2</v>
+        <f>'معلومات الطلاب'!E5</f>
+        <v>1</v>
       </c>
       <c r="E6" t="str">
-        <f>'معلومات الطلاب'!F6</f>
+        <f>'معلومات الطلاب'!F5</f>
         <v>رياضيات</v>
       </c>
       <c r="F6" s="2">
@@ -3267,23 +3293,23 @@
     </row>
     <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
-        <f>'معلومات الطلاب'!A7</f>
-        <v>1005</v>
+        <f>'معلومات الطلاب'!A6</f>
+        <v>1004</v>
       </c>
       <c r="B7" t="str">
-        <f>'معلومات الطلاب'!B7</f>
-        <v>مريم علي الشهري</v>
+        <f>'معلومات الطلاب'!B6</f>
+        <v>شهد فهد القحطاني</v>
       </c>
       <c r="C7" t="str">
-        <f>'معلومات الطلاب'!D7</f>
+        <f>'معلومات الطلاب'!D6</f>
         <v>الخامس</v>
       </c>
       <c r="D7">
-        <f>'معلومات الطلاب'!E7</f>
+        <f>'معلومات الطلاب'!E6</f>
         <v>2</v>
       </c>
       <c r="E7" t="str">
-        <f>'معلومات الطلاب'!F7</f>
+        <f>'معلومات الطلاب'!F6</f>
         <v>رياضيات</v>
       </c>
       <c r="F7" s="2">
@@ -3363,24 +3389,24 @@
     </row>
     <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8">
-        <f>'معلومات الطلاب'!A8</f>
-        <v>1006</v>
+        <f>'معلومات الطلاب'!A7</f>
+        <v>1005</v>
       </c>
       <c r="B8" t="str">
-        <f>'معلومات الطلاب'!B8</f>
-        <v>أروى محمد الدوسري</v>
+        <f>'معلومات الطلاب'!B7</f>
+        <v>مريم علي الشهري</v>
       </c>
       <c r="C8" t="str">
-        <f>'معلومات الطلاب'!D8</f>
-        <v>السادس</v>
+        <f>'معلومات الطلاب'!D7</f>
+        <v>الخامس</v>
       </c>
       <c r="D8">
-        <f>'معلومات الطلاب'!E8</f>
-        <v>1</v>
+        <f>'معلومات الطلاب'!E7</f>
+        <v>2</v>
       </c>
       <c r="E8" t="str">
-        <f>'معلومات الطلاب'!F8</f>
-        <v>علوم</v>
+        <f>'معلومات الطلاب'!F7</f>
+        <v>رياضيات</v>
       </c>
       <c r="F8" s="2">
         <v>2</v>
@@ -3459,23 +3485,23 @@
     </row>
     <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
-        <f>'معلومات الطلاب'!A9</f>
-        <v>1007</v>
+        <f>'معلومات الطلاب'!A8</f>
+        <v>1006</v>
       </c>
       <c r="B9" t="str">
-        <f>'معلومات الطلاب'!B9</f>
-        <v>لجين حمد العبد الله</v>
+        <f>'معلومات الطلاب'!B8</f>
+        <v>أروى محمد الدوسري</v>
       </c>
       <c r="C9" t="str">
-        <f>'معلومات الطلاب'!D9</f>
+        <f>'معلومات الطلاب'!D8</f>
         <v>السادس</v>
       </c>
       <c r="D9">
-        <f>'معلومات الطلاب'!E9</f>
+        <f>'معلومات الطلاب'!E8</f>
         <v>1</v>
       </c>
       <c r="E9" t="str">
-        <f>'معلومات الطلاب'!F9</f>
+        <f>'معلومات الطلاب'!F8</f>
         <v>علوم</v>
       </c>
       <c r="F9" s="2">
@@ -3555,23 +3581,23 @@
     </row>
     <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10">
-        <f>'معلومات الطلاب'!A10</f>
-        <v>1008</v>
+        <f>'معلومات الطلاب'!A9</f>
+        <v>1007</v>
       </c>
       <c r="B10" t="str">
-        <f>'معلومات الطلاب'!B10</f>
-        <v>جود سلطان العتيبي</v>
+        <f>'معلومات الطلاب'!B9</f>
+        <v>لجين حمد العبد الله</v>
       </c>
       <c r="C10" t="str">
-        <f>'معلومات الطلاب'!D10</f>
+        <f>'معلومات الطلاب'!D9</f>
         <v>السادس</v>
       </c>
       <c r="D10">
-        <f>'معلومات الطلاب'!E10</f>
+        <f>'معلومات الطلاب'!E9</f>
         <v>1</v>
       </c>
       <c r="E10" t="str">
-        <f>'معلومات الطلاب'!F10</f>
+        <f>'معلومات الطلاب'!F9</f>
         <v>علوم</v>
       </c>
       <c r="F10" s="2">
@@ -3651,23 +3677,23 @@
     </row>
     <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11">
-        <f>'معلومات الطلاب'!A11</f>
-        <v>1009</v>
+        <f>'معلومات الطلاب'!A10</f>
+        <v>1008</v>
       </c>
       <c r="B11" t="str">
-        <f>'معلومات الطلاب'!B11</f>
-        <v>حلا يوسف المطر</v>
+        <f>'معلومات الطلاب'!B10</f>
+        <v>جود سلطان العتيبي</v>
       </c>
       <c r="C11" t="str">
-        <f>'معلومات الطلاب'!D11</f>
+        <f>'معلومات الطلاب'!D10</f>
         <v>السادس</v>
       </c>
       <c r="D11">
-        <f>'معلومات الطلاب'!E11</f>
-        <v>2</v>
+        <f>'معلومات الطلاب'!E10</f>
+        <v>1</v>
       </c>
       <c r="E11" t="str">
-        <f>'معلومات الطلاب'!F11</f>
+        <f>'معلومات الطلاب'!F10</f>
         <v>علوم</v>
       </c>
       <c r="F11" s="2">
@@ -3747,23 +3773,23 @@
     </row>
     <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
-        <f>'معلومات الطلاب'!A12</f>
-        <v>1010</v>
+        <f>'معلومات الطلاب'!A11</f>
+        <v>1009</v>
       </c>
       <c r="B12" t="str">
-        <f>'معلومات الطلاب'!B12</f>
-        <v>غادة إبراهيم الزهراني</v>
+        <f>'معلومات الطلاب'!B11</f>
+        <v>حلا يوسف المطر</v>
       </c>
       <c r="C12" t="str">
-        <f>'معلومات الطلاب'!D12</f>
+        <f>'معلومات الطلاب'!D11</f>
         <v>السادس</v>
       </c>
       <c r="D12">
-        <f>'معلومات الطلاب'!E12</f>
+        <f>'معلومات الطلاب'!E11</f>
         <v>2</v>
       </c>
       <c r="E12" t="str">
-        <f>'معلومات الطلاب'!F12</f>
+        <f>'معلومات الطلاب'!F11</f>
         <v>علوم</v>
       </c>
       <c r="F12" s="2">
@@ -3843,23 +3869,23 @@
     </row>
     <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13">
-        <f>'معلومات الطلاب'!A13</f>
-        <v>1011</v>
+        <f>'معلومات الطلاب'!A12</f>
+        <v>1010</v>
       </c>
       <c r="B13" t="str">
-        <f>'معلومات الطلاب'!B13</f>
-        <v>نوهان ثروت علي</v>
+        <f>'معلومات الطلاب'!B12</f>
+        <v>غادة إبراهيم الزهراني</v>
       </c>
       <c r="C13" t="str">
-        <f>'معلومات الطلاب'!D13</f>
+        <f>'معلومات الطلاب'!D12</f>
         <v>السادس</v>
       </c>
       <c r="D13">
-        <f>'معلومات الطلاب'!E13</f>
+        <f>'معلومات الطلاب'!E12</f>
         <v>2</v>
       </c>
       <c r="E13" t="str">
-        <f>'معلومات الطلاب'!F13</f>
+        <f>'معلومات الطلاب'!F12</f>
         <v>علوم</v>
       </c>
       <c r="F13" s="2">
@@ -3939,46 +3965,46 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14">
+        <f>'معلومات الطلاب'!A13</f>
+        <v>1011</v>
+      </c>
+      <c r="B14" t="str">
+        <f>'معلومات الطلاب'!B13</f>
+        <v>نوهان ثروت علي</v>
+      </c>
+      <c r="C14" t="str">
+        <f>'معلومات الطلاب'!D13</f>
+        <v>السادس</v>
+      </c>
+      <c r="D14">
+        <f>'معلومات الطلاب'!E13</f>
+        <v>2</v>
+      </c>
+      <c r="E14" t="str">
+        <f>'معلومات الطلاب'!F13</f>
+        <v>علوم</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15">
         <f>'معلومات الطلاب'!A14</f>
         <v>1012</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B15" t="str">
         <f>'معلومات الطلاب'!B14</f>
         <v>سلمى محمد على يوسف</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C15" t="str">
         <f>'معلومات الطلاب'!D14</f>
         <v>السادس</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <f>'معلومات الطلاب'!E14</f>
         <v>1</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E15" t="str">
         <f>'معلومات الطلاب'!F14</f>
         <v>لغتي</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <f>'معلومات الطلاب'!A15</f>
-        <v>0</v>
-      </c>
-      <c r="B15">
-        <f>'معلومات الطلاب'!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <f>'معلومات الطلاب'!D15</f>
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <f>'معلومات الطلاب'!E15</f>
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f>'معلومات الطلاب'!F15</f>
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -4389,9 +4415,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="9" max="9" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I7" t="e">
+        <f>'[1]الفصل الدراسي الاول'!A5</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/students_system.xlsx
+++ b/students_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="22980" windowHeight="9288" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="معلومات الطلاب" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="60">
   <si>
     <t>رقم الطالبة</t>
   </si>
@@ -192,12 +192,21 @@
   <si>
     <t>لغتي</t>
   </si>
+  <si>
+    <t>القسم</t>
+  </si>
+  <si>
+    <t>عام</t>
+  </si>
+  <si>
+    <t>تحفيظ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +249,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -255,7 +275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -320,11 +340,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
@@ -353,11 +386,63 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFC4C7C5"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC4C7C5"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC4C7C5"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4C7C5"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="medium">
@@ -764,25 +849,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:G16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
-  <autoFilter ref="A2:G16"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="رقم الطالبة" dataDxfId="12"/>
-    <tableColumn id="2" name="اسم الطالبة" dataDxfId="11"/>
-    <tableColumn id="3" name="السنة الدراسية" dataDxfId="10"/>
-    <tableColumn id="4" name="الصف الدراسي" dataDxfId="9"/>
-    <tableColumn id="5" name="الفصل" dataDxfId="8"/>
-    <tableColumn id="6" name="المادة" dataDxfId="7"/>
-    <tableColumn id="7" name="اسم المعلمة" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="الجدول3" displayName="الجدول3" ref="A2:H21" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16">
+  <autoFilter ref="A2:H21"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="رقم الطالبة" dataDxfId="15"/>
+    <tableColumn id="2" name="اسم الطالبة" dataDxfId="14"/>
+    <tableColumn id="3" name="السنة الدراسية" dataDxfId="13"/>
+    <tableColumn id="4" name="الصف الدراسي" dataDxfId="12"/>
+    <tableColumn id="5" name="الفصل" dataDxfId="11"/>
+    <tableColumn id="6" name="المادة" dataDxfId="10"/>
+    <tableColumn id="7" name="اسم المعلمة" dataDxfId="9"/>
+    <tableColumn id="8" name="القسم" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="الجدول1" displayName="الجدول1" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
-  <autoFilter ref="A3:AB411"/>
-  <tableColumns count="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="الجدول1" displayName="الجدول1" ref="A3:AC411" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
+  <autoFilter ref="A3:AC411"/>
+  <tableColumns count="29">
     <tableColumn id="1" name="رقم"/>
     <tableColumn id="2" name="الطالبة"/>
     <tableColumn id="3" name="الصف الدراسي"/>
@@ -811,15 +897,18 @@
     <tableColumn id="26" name="النسبة المئوية"/>
     <tableColumn id="27" name="التقدير العام"/>
     <tableColumn id="28" name="حالة الخطة العلاجية"/>
+    <tableColumn id="29" name="القسم" dataDxfId="1">
+      <calculatedColumnFormula>'معلومات الطلاب'!H3</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="الجدول13" displayName="الجدول13" ref="A3:AB411" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A3:AB411"/>
-  <tableColumns count="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="الجدول13" displayName="الجدول13" ref="A3:AC411" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+  <autoFilter ref="A3:AC411"/>
+  <tableColumns count="29">
     <tableColumn id="1" name="رقم"/>
     <tableColumn id="2" name="الطالبة"/>
     <tableColumn id="3" name="الصف الدراسي"/>
@@ -848,6 +937,9 @@
     <tableColumn id="26" name="النسبة المئوية"/>
     <tableColumn id="27" name="التقدير العام"/>
     <tableColumn id="28" name="حالة الخطة العلاجية"/>
+    <tableColumn id="29" name="القسم" dataDxfId="0">
+      <calculatedColumnFormula>'معلومات الطلاب'!H4</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1140,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
@@ -1152,7 +1244,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>24</v>
       </c>
@@ -1163,7 +1255,7 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1185,8 +1277,11 @@
       <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H2" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1001</v>
       </c>
@@ -1208,8 +1303,11 @@
       <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H3" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1002</v>
       </c>
@@ -1231,8 +1329,11 @@
       <c r="G4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H4" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>1003</v>
       </c>
@@ -1254,8 +1355,11 @@
       <c r="G5" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H5" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>1004</v>
       </c>
@@ -1277,8 +1381,11 @@
       <c r="G6" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H6" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>1005</v>
       </c>
@@ -1300,8 +1407,11 @@
       <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H7" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>1006</v>
       </c>
@@ -1323,8 +1433,11 @@
       <c r="G8" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H8" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>1007</v>
       </c>
@@ -1346,8 +1459,11 @@
       <c r="G9" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H9" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>1008</v>
       </c>
@@ -1369,8 +1485,11 @@
       <c r="G10" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H10" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>1009</v>
       </c>
@@ -1392,8 +1511,11 @@
       <c r="G11" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H11" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>1010</v>
       </c>
@@ -1415,8 +1537,11 @@
       <c r="G12" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H12" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1011</v>
       </c>
@@ -1438,8 +1563,11 @@
       <c r="G13" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H13" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1012</v>
       </c>
@@ -1461,22 +1589,77 @@
       <c r="G14" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H14" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1492,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AG37"/>
+  <dimension ref="A2:AG411"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -1635,7 +1818,9 @@
       <c r="AB3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC3" s="1"/>
+      <c r="AC3" s="13" t="s">
+        <v>57</v>
+      </c>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -1736,6 +1921,10 @@
         <f>IF(Z4&lt;0.6,"متعثر",IF(Z4&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
         <v>لا يحتاج متابعة</v>
       </c>
+      <c r="AC4" t="str">
+        <f>'معلومات الطلاب'!H3</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -1832,6 +2021,10 @@
         <f t="shared" ref="AB5:AB13" si="4">IF(Z5&lt;0.6,"متعثر",IF(Z5&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC5" t="str">
+        <f>'معلومات الطلاب'!H4</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -1928,6 +2121,10 @@
         <f t="shared" si="4"/>
         <v>متعثر</v>
       </c>
+      <c r="AC6" t="str">
+        <f>'معلومات الطلاب'!H5</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -2024,6 +2221,10 @@
         <f t="shared" si="4"/>
         <v>متعثر</v>
       </c>
+      <c r="AC7" t="str">
+        <f>'معلومات الطلاب'!H6</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -2120,6 +2321,10 @@
         <f t="shared" si="4"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC8" t="str">
+        <f>'معلومات الطلاب'!H7</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -2216,6 +2421,10 @@
         <f t="shared" si="4"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC9" t="str">
+        <f>'معلومات الطلاب'!H8</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -2312,6 +2521,10 @@
         <f t="shared" si="4"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC10" t="str">
+        <f>'معلومات الطلاب'!H9</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -2408,6 +2621,10 @@
         <f t="shared" si="4"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC11" t="str">
+        <f>'معلومات الطلاب'!H10</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -2504,6 +2721,10 @@
         <f t="shared" si="4"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC12" t="str">
+        <f>'معلومات الطلاب'!H11</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -2600,6 +2821,10 @@
         <f t="shared" si="4"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC13" t="str">
+        <f>'معلومات الطلاب'!H12</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="14" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -2696,6 +2921,10 @@
         <f t="shared" ref="AB14" si="9">IF(Z14&lt;0.6,"متعثر",IF(Z14&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC14" t="str">
+        <f>'معلومات الطلاب'!H13</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -2706,9 +2935,78 @@
         <f>'معلومات الطلاب'!B14</f>
         <v>سلمى محمد على يوسف</v>
       </c>
-    </row>
-    <row r="26" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC15" t="str">
+        <f>'معلومات الطلاب'!H14</f>
+        <v>عام</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AC16">
+        <f>'معلومات الطلاب'!H15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC17">
+        <f>'معلومات الطلاب'!H16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC18">
+        <f>'معلومات الطلاب'!H17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC19">
+        <f>'معلومات الطلاب'!H18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC20">
+        <f>'معلومات الطلاب'!H19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC21">
+        <f>'معلومات الطلاب'!H20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC22">
+        <f>'معلومات الطلاب'!H21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC23">
+        <f>'معلومات الطلاب'!H22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC24">
+        <f>'معلومات الطلاب'!H23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC25">
+        <f>'معلومات الطلاب'!H24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC26">
+        <f>'معلومات الطلاب'!H25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2719,8 +3017,12 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC27">
+        <f>'معلومات الطلاب'!H26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -2731,8 +3033,12 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC28">
+        <f>'معلومات الطلاب'!H27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -2743,8 +3049,12 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC29">
+        <f>'معلومات الطلاب'!H28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -2755,8 +3065,12 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC30">
+        <f>'معلومات الطلاب'!H29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -2767,8 +3081,12 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC31">
+        <f>'معلومات الطلاب'!H30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -2779,8 +3097,12 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC32">
+        <f>'معلومات الطلاب'!H31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -2791,8 +3113,12 @@
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC33">
+        <f>'معلومات الطلاب'!H32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -2803,8 +3129,12 @@
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC34">
+        <f>'معلومات الطلاب'!H33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -2815,8 +3145,12 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC35">
+        <f>'معلومات الطلاب'!H34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -2827,8 +3161,12 @@
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC36">
+        <f>'معلومات الطلاب'!H35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -2839,6 +3177,2254 @@
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
+      <c r="AC37">
+        <f>'معلومات الطلاب'!H36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC38">
+        <f>'معلومات الطلاب'!H37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC39">
+        <f>'معلومات الطلاب'!H38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC40">
+        <f>'معلومات الطلاب'!H39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC41">
+        <f>'معلومات الطلاب'!H40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC42">
+        <f>'معلومات الطلاب'!H41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC43">
+        <f>'معلومات الطلاب'!H42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC44">
+        <f>'معلومات الطلاب'!H43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC45">
+        <f>'معلومات الطلاب'!H44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC46">
+        <f>'معلومات الطلاب'!H45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC47">
+        <f>'معلومات الطلاب'!H46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC48">
+        <f>'معلومات الطلاب'!H47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC49">
+        <f>'معلومات الطلاب'!H48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC50">
+        <f>'معلومات الطلاب'!H49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC51">
+        <f>'معلومات الطلاب'!H50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC52">
+        <f>'معلومات الطلاب'!H51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC53">
+        <f>'معلومات الطلاب'!H52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC54">
+        <f>'معلومات الطلاب'!H53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC55">
+        <f>'معلومات الطلاب'!H54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC56">
+        <f>'معلومات الطلاب'!H55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC57">
+        <f>'معلومات الطلاب'!H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC58">
+        <f>'معلومات الطلاب'!H57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC59">
+        <f>'معلومات الطلاب'!H58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC60">
+        <f>'معلومات الطلاب'!H59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC61">
+        <f>'معلومات الطلاب'!H60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC62">
+        <f>'معلومات الطلاب'!H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC63">
+        <f>'معلومات الطلاب'!H62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC64">
+        <f>'معلومات الطلاب'!H63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC65">
+        <f>'معلومات الطلاب'!H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC66">
+        <f>'معلومات الطلاب'!H65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC67">
+        <f>'معلومات الطلاب'!H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC68">
+        <f>'معلومات الطلاب'!H67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC69">
+        <f>'معلومات الطلاب'!H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC70">
+        <f>'معلومات الطلاب'!H69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC71">
+        <f>'معلومات الطلاب'!H70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC72">
+        <f>'معلومات الطلاب'!H71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC73">
+        <f>'معلومات الطلاب'!H72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC74">
+        <f>'معلومات الطلاب'!H73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC75">
+        <f>'معلومات الطلاب'!H74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC76">
+        <f>'معلومات الطلاب'!H75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC77">
+        <f>'معلومات الطلاب'!H76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC78">
+        <f>'معلومات الطلاب'!H77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC79">
+        <f>'معلومات الطلاب'!H78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC80">
+        <f>'معلومات الطلاب'!H79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC81">
+        <f>'معلومات الطلاب'!H80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC82">
+        <f>'معلومات الطلاب'!H81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC83">
+        <f>'معلومات الطلاب'!H82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC84">
+        <f>'معلومات الطلاب'!H83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC85">
+        <f>'معلومات الطلاب'!H84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC86">
+        <f>'معلومات الطلاب'!H85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC87">
+        <f>'معلومات الطلاب'!H86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC88">
+        <f>'معلومات الطلاب'!H87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC89">
+        <f>'معلومات الطلاب'!H88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC90">
+        <f>'معلومات الطلاب'!H89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC91">
+        <f>'معلومات الطلاب'!H90</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC92">
+        <f>'معلومات الطلاب'!H91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC93">
+        <f>'معلومات الطلاب'!H92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC94">
+        <f>'معلومات الطلاب'!H93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC95">
+        <f>'معلومات الطلاب'!H94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC96">
+        <f>'معلومات الطلاب'!H95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC97">
+        <f>'معلومات الطلاب'!H96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC98">
+        <f>'معلومات الطلاب'!H97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC99">
+        <f>'معلومات الطلاب'!H98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC100">
+        <f>'معلومات الطلاب'!H99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC101">
+        <f>'معلومات الطلاب'!H100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC102">
+        <f>'معلومات الطلاب'!H101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC103">
+        <f>'معلومات الطلاب'!H102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC104">
+        <f>'معلومات الطلاب'!H103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC105">
+        <f>'معلومات الطلاب'!H104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC106">
+        <f>'معلومات الطلاب'!H105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC107">
+        <f>'معلومات الطلاب'!H106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC108">
+        <f>'معلومات الطلاب'!H107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC109">
+        <f>'معلومات الطلاب'!H108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC110">
+        <f>'معلومات الطلاب'!H109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC111">
+        <f>'معلومات الطلاب'!H110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC112">
+        <f>'معلومات الطلاب'!H111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC113">
+        <f>'معلومات الطلاب'!H112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC114">
+        <f>'معلومات الطلاب'!H113</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC115">
+        <f>'معلومات الطلاب'!H114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC116">
+        <f>'معلومات الطلاب'!H115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC117">
+        <f>'معلومات الطلاب'!H116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC118">
+        <f>'معلومات الطلاب'!H117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC119">
+        <f>'معلومات الطلاب'!H118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC120">
+        <f>'معلومات الطلاب'!H119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC121">
+        <f>'معلومات الطلاب'!H120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC122">
+        <f>'معلومات الطلاب'!H121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC123">
+        <f>'معلومات الطلاب'!H122</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC124">
+        <f>'معلومات الطلاب'!H123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC125">
+        <f>'معلومات الطلاب'!H124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC126">
+        <f>'معلومات الطلاب'!H125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC127">
+        <f>'معلومات الطلاب'!H126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC128">
+        <f>'معلومات الطلاب'!H127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC129">
+        <f>'معلومات الطلاب'!H128</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC130">
+        <f>'معلومات الطلاب'!H129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC131">
+        <f>'معلومات الطلاب'!H130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC132">
+        <f>'معلومات الطلاب'!H131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC133">
+        <f>'معلومات الطلاب'!H132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC134">
+        <f>'معلومات الطلاب'!H133</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC135">
+        <f>'معلومات الطلاب'!H134</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC136">
+        <f>'معلومات الطلاب'!H135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC137">
+        <f>'معلومات الطلاب'!H136</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC138">
+        <f>'معلومات الطلاب'!H137</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC139">
+        <f>'معلومات الطلاب'!H138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC140">
+        <f>'معلومات الطلاب'!H139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC141">
+        <f>'معلومات الطلاب'!H140</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC142">
+        <f>'معلومات الطلاب'!H141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC143">
+        <f>'معلومات الطلاب'!H142</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC144">
+        <f>'معلومات الطلاب'!H143</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC145">
+        <f>'معلومات الطلاب'!H144</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC146">
+        <f>'معلومات الطلاب'!H145</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC147">
+        <f>'معلومات الطلاب'!H146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC148">
+        <f>'معلومات الطلاب'!H147</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC149">
+        <f>'معلومات الطلاب'!H148</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC150">
+        <f>'معلومات الطلاب'!H149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC151">
+        <f>'معلومات الطلاب'!H150</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC152">
+        <f>'معلومات الطلاب'!H151</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC153">
+        <f>'معلومات الطلاب'!H152</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC154">
+        <f>'معلومات الطلاب'!H153</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC155">
+        <f>'معلومات الطلاب'!H154</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC156">
+        <f>'معلومات الطلاب'!H155</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC157">
+        <f>'معلومات الطلاب'!H156</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC158">
+        <f>'معلومات الطلاب'!H157</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC159">
+        <f>'معلومات الطلاب'!H158</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC160">
+        <f>'معلومات الطلاب'!H159</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC161">
+        <f>'معلومات الطلاب'!H160</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC162">
+        <f>'معلومات الطلاب'!H161</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC163">
+        <f>'معلومات الطلاب'!H162</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC164">
+        <f>'معلومات الطلاب'!H163</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC165">
+        <f>'معلومات الطلاب'!H164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC166">
+        <f>'معلومات الطلاب'!H165</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC167">
+        <f>'معلومات الطلاب'!H166</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC168">
+        <f>'معلومات الطلاب'!H167</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC169">
+        <f>'معلومات الطلاب'!H168</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC170">
+        <f>'معلومات الطلاب'!H169</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC171">
+        <f>'معلومات الطلاب'!H170</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC172">
+        <f>'معلومات الطلاب'!H171</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC173">
+        <f>'معلومات الطلاب'!H172</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC174">
+        <f>'معلومات الطلاب'!H173</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC175">
+        <f>'معلومات الطلاب'!H174</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC176">
+        <f>'معلومات الطلاب'!H175</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC177">
+        <f>'معلومات الطلاب'!H176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC178">
+        <f>'معلومات الطلاب'!H177</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC179">
+        <f>'معلومات الطلاب'!H178</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC180">
+        <f>'معلومات الطلاب'!H179</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC181">
+        <f>'معلومات الطلاب'!H180</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC182">
+        <f>'معلومات الطلاب'!H181</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC183">
+        <f>'معلومات الطلاب'!H182</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC184">
+        <f>'معلومات الطلاب'!H183</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC185">
+        <f>'معلومات الطلاب'!H184</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC186">
+        <f>'معلومات الطلاب'!H185</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC187">
+        <f>'معلومات الطلاب'!H186</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC188">
+        <f>'معلومات الطلاب'!H187</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC189">
+        <f>'معلومات الطلاب'!H188</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC190">
+        <f>'معلومات الطلاب'!H189</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC191">
+        <f>'معلومات الطلاب'!H190</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC192">
+        <f>'معلومات الطلاب'!H191</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC193">
+        <f>'معلومات الطلاب'!H192</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC194">
+        <f>'معلومات الطلاب'!H193</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC195">
+        <f>'معلومات الطلاب'!H194</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC196">
+        <f>'معلومات الطلاب'!H195</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC197">
+        <f>'معلومات الطلاب'!H196</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC198">
+        <f>'معلومات الطلاب'!H197</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC199">
+        <f>'معلومات الطلاب'!H198</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC200">
+        <f>'معلومات الطلاب'!H199</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC201">
+        <f>'معلومات الطلاب'!H200</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC202">
+        <f>'معلومات الطلاب'!H201</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC203">
+        <f>'معلومات الطلاب'!H202</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC204">
+        <f>'معلومات الطلاب'!H203</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC205">
+        <f>'معلومات الطلاب'!H204</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC206">
+        <f>'معلومات الطلاب'!H205</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC207">
+        <f>'معلومات الطلاب'!H206</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC208">
+        <f>'معلومات الطلاب'!H207</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC209">
+        <f>'معلومات الطلاب'!H208</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC210">
+        <f>'معلومات الطلاب'!H209</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC211">
+        <f>'معلومات الطلاب'!H210</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC212">
+        <f>'معلومات الطلاب'!H211</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC213">
+        <f>'معلومات الطلاب'!H212</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC214">
+        <f>'معلومات الطلاب'!H213</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC215">
+        <f>'معلومات الطلاب'!H214</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC216">
+        <f>'معلومات الطلاب'!H215</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC217">
+        <f>'معلومات الطلاب'!H216</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC218">
+        <f>'معلومات الطلاب'!H217</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC219">
+        <f>'معلومات الطلاب'!H218</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC220">
+        <f>'معلومات الطلاب'!H219</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC221">
+        <f>'معلومات الطلاب'!H220</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC222">
+        <f>'معلومات الطلاب'!H221</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC223">
+        <f>'معلومات الطلاب'!H222</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC224">
+        <f>'معلومات الطلاب'!H223</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC225">
+        <f>'معلومات الطلاب'!H224</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC226">
+        <f>'معلومات الطلاب'!H225</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC227">
+        <f>'معلومات الطلاب'!H226</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC228">
+        <f>'معلومات الطلاب'!H227</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC229">
+        <f>'معلومات الطلاب'!H228</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC230">
+        <f>'معلومات الطلاب'!H229</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC231">
+        <f>'معلومات الطلاب'!H230</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC232">
+        <f>'معلومات الطلاب'!H231</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC233">
+        <f>'معلومات الطلاب'!H232</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC234">
+        <f>'معلومات الطلاب'!H233</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC235">
+        <f>'معلومات الطلاب'!H234</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC236">
+        <f>'معلومات الطلاب'!H235</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC237">
+        <f>'معلومات الطلاب'!H236</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC238">
+        <f>'معلومات الطلاب'!H237</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC239">
+        <f>'معلومات الطلاب'!H238</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC240">
+        <f>'معلومات الطلاب'!H239</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC241">
+        <f>'معلومات الطلاب'!H240</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC242">
+        <f>'معلومات الطلاب'!H241</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC243">
+        <f>'معلومات الطلاب'!H242</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC244">
+        <f>'معلومات الطلاب'!H243</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC245">
+        <f>'معلومات الطلاب'!H244</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC246">
+        <f>'معلومات الطلاب'!H245</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC247">
+        <f>'معلومات الطلاب'!H246</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC248">
+        <f>'معلومات الطلاب'!H247</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC249">
+        <f>'معلومات الطلاب'!H248</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC250">
+        <f>'معلومات الطلاب'!H249</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC251">
+        <f>'معلومات الطلاب'!H250</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC252">
+        <f>'معلومات الطلاب'!H251</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC253">
+        <f>'معلومات الطلاب'!H252</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC254">
+        <f>'معلومات الطلاب'!H253</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC255">
+        <f>'معلومات الطلاب'!H254</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC256">
+        <f>'معلومات الطلاب'!H255</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC257">
+        <f>'معلومات الطلاب'!H256</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC258">
+        <f>'معلومات الطلاب'!H257</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC259">
+        <f>'معلومات الطلاب'!H258</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC260">
+        <f>'معلومات الطلاب'!H259</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC261">
+        <f>'معلومات الطلاب'!H260</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC262">
+        <f>'معلومات الطلاب'!H261</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC263">
+        <f>'معلومات الطلاب'!H262</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC264">
+        <f>'معلومات الطلاب'!H263</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC265">
+        <f>'معلومات الطلاب'!H264</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC266">
+        <f>'معلومات الطلاب'!H265</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC267">
+        <f>'معلومات الطلاب'!H266</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC268">
+        <f>'معلومات الطلاب'!H267</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC269">
+        <f>'معلومات الطلاب'!H268</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC270">
+        <f>'معلومات الطلاب'!H269</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC271">
+        <f>'معلومات الطلاب'!H270</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC272">
+        <f>'معلومات الطلاب'!H271</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC273">
+        <f>'معلومات الطلاب'!H272</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC274">
+        <f>'معلومات الطلاب'!H273</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC275">
+        <f>'معلومات الطلاب'!H274</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC276">
+        <f>'معلومات الطلاب'!H275</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC277">
+        <f>'معلومات الطلاب'!H276</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC278">
+        <f>'معلومات الطلاب'!H277</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC279">
+        <f>'معلومات الطلاب'!H278</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC280">
+        <f>'معلومات الطلاب'!H279</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC281">
+        <f>'معلومات الطلاب'!H280</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC282">
+        <f>'معلومات الطلاب'!H281</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC283">
+        <f>'معلومات الطلاب'!H282</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC284">
+        <f>'معلومات الطلاب'!H283</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC285">
+        <f>'معلومات الطلاب'!H284</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC286">
+        <f>'معلومات الطلاب'!H285</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC287">
+        <f>'معلومات الطلاب'!H286</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC288">
+        <f>'معلومات الطلاب'!H287</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC289">
+        <f>'معلومات الطلاب'!H288</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC290">
+        <f>'معلومات الطلاب'!H289</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC291">
+        <f>'معلومات الطلاب'!H290</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC292">
+        <f>'معلومات الطلاب'!H291</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC293">
+        <f>'معلومات الطلاب'!H292</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC294">
+        <f>'معلومات الطلاب'!H293</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC295">
+        <f>'معلومات الطلاب'!H294</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC296">
+        <f>'معلومات الطلاب'!H295</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC297">
+        <f>'معلومات الطلاب'!H296</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC298">
+        <f>'معلومات الطلاب'!H297</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC299">
+        <f>'معلومات الطلاب'!H298</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC300">
+        <f>'معلومات الطلاب'!H299</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC301">
+        <f>'معلومات الطلاب'!H300</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC302">
+        <f>'معلومات الطلاب'!H301</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC303">
+        <f>'معلومات الطلاب'!H302</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC304">
+        <f>'معلومات الطلاب'!H303</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC305">
+        <f>'معلومات الطلاب'!H304</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC306">
+        <f>'معلومات الطلاب'!H305</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC307">
+        <f>'معلومات الطلاب'!H306</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC308">
+        <f>'معلومات الطلاب'!H307</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC309">
+        <f>'معلومات الطلاب'!H308</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC310">
+        <f>'معلومات الطلاب'!H309</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC311">
+        <f>'معلومات الطلاب'!H310</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC312">
+        <f>'معلومات الطلاب'!H311</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC313">
+        <f>'معلومات الطلاب'!H312</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC314">
+        <f>'معلومات الطلاب'!H313</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC315">
+        <f>'معلومات الطلاب'!H314</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC316">
+        <f>'معلومات الطلاب'!H315</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC317">
+        <f>'معلومات الطلاب'!H316</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC318">
+        <f>'معلومات الطلاب'!H317</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC319">
+        <f>'معلومات الطلاب'!H318</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC320">
+        <f>'معلومات الطلاب'!H319</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC321">
+        <f>'معلومات الطلاب'!H320</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC322">
+        <f>'معلومات الطلاب'!H321</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC323">
+        <f>'معلومات الطلاب'!H322</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC324">
+        <f>'معلومات الطلاب'!H323</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC325">
+        <f>'معلومات الطلاب'!H324</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC326">
+        <f>'معلومات الطلاب'!H325</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC327">
+        <f>'معلومات الطلاب'!H326</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC328">
+        <f>'معلومات الطلاب'!H327</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC329">
+        <f>'معلومات الطلاب'!H328</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC330">
+        <f>'معلومات الطلاب'!H329</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC331">
+        <f>'معلومات الطلاب'!H330</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC332">
+        <f>'معلومات الطلاب'!H331</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC333">
+        <f>'معلومات الطلاب'!H332</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC334">
+        <f>'معلومات الطلاب'!H333</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC335">
+        <f>'معلومات الطلاب'!H334</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC336">
+        <f>'معلومات الطلاب'!H335</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC337">
+        <f>'معلومات الطلاب'!H336</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC338">
+        <f>'معلومات الطلاب'!H337</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC339">
+        <f>'معلومات الطلاب'!H338</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC340">
+        <f>'معلومات الطلاب'!H339</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC341">
+        <f>'معلومات الطلاب'!H340</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC342">
+        <f>'معلومات الطلاب'!H341</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC343">
+        <f>'معلومات الطلاب'!H342</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC344">
+        <f>'معلومات الطلاب'!H343</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC345">
+        <f>'معلومات الطلاب'!H344</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC346">
+        <f>'معلومات الطلاب'!H345</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC347">
+        <f>'معلومات الطلاب'!H346</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC348">
+        <f>'معلومات الطلاب'!H347</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC349">
+        <f>'معلومات الطلاب'!H348</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC350">
+        <f>'معلومات الطلاب'!H349</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC351">
+        <f>'معلومات الطلاب'!H350</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC352">
+        <f>'معلومات الطلاب'!H351</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC353">
+        <f>'معلومات الطلاب'!H352</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC354">
+        <f>'معلومات الطلاب'!H353</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC355">
+        <f>'معلومات الطلاب'!H354</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC356">
+        <f>'معلومات الطلاب'!H355</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC357">
+        <f>'معلومات الطلاب'!H356</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC358">
+        <f>'معلومات الطلاب'!H357</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC359">
+        <f>'معلومات الطلاب'!H358</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC360">
+        <f>'معلومات الطلاب'!H359</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC361">
+        <f>'معلومات الطلاب'!H360</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC362">
+        <f>'معلومات الطلاب'!H361</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC363">
+        <f>'معلومات الطلاب'!H362</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC364">
+        <f>'معلومات الطلاب'!H363</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC365">
+        <f>'معلومات الطلاب'!H364</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC366">
+        <f>'معلومات الطلاب'!H365</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC367">
+        <f>'معلومات الطلاب'!H366</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC368">
+        <f>'معلومات الطلاب'!H367</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC369">
+        <f>'معلومات الطلاب'!H368</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC370">
+        <f>'معلومات الطلاب'!H369</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC371">
+        <f>'معلومات الطلاب'!H370</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC372">
+        <f>'معلومات الطلاب'!H371</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC373">
+        <f>'معلومات الطلاب'!H372</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC374">
+        <f>'معلومات الطلاب'!H373</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC375">
+        <f>'معلومات الطلاب'!H374</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC376">
+        <f>'معلومات الطلاب'!H375</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC377">
+        <f>'معلومات الطلاب'!H376</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC378">
+        <f>'معلومات الطلاب'!H377</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC379">
+        <f>'معلومات الطلاب'!H378</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC380">
+        <f>'معلومات الطلاب'!H379</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC381">
+        <f>'معلومات الطلاب'!H380</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC382">
+        <f>'معلومات الطلاب'!H381</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC383">
+        <f>'معلومات الطلاب'!H382</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC384">
+        <f>'معلومات الطلاب'!H383</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC385">
+        <f>'معلومات الطلاب'!H384</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC386">
+        <f>'معلومات الطلاب'!H385</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC387">
+        <f>'معلومات الطلاب'!H386</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC388">
+        <f>'معلومات الطلاب'!H387</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC389">
+        <f>'معلومات الطلاب'!H388</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC390">
+        <f>'معلومات الطلاب'!H389</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC391">
+        <f>'معلومات الطلاب'!H390</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC392">
+        <f>'معلومات الطلاب'!H391</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC393">
+        <f>'معلومات الطلاب'!H392</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC394">
+        <f>'معلومات الطلاب'!H393</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC395">
+        <f>'معلومات الطلاب'!H394</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC396">
+        <f>'معلومات الطلاب'!H395</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC397">
+        <f>'معلومات الطلاب'!H396</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC398">
+        <f>'معلومات الطلاب'!H397</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC399">
+        <f>'معلومات الطلاب'!H398</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC400">
+        <f>'معلومات الطلاب'!H399</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC401">
+        <f>'معلومات الطلاب'!H400</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC402">
+        <f>'معلومات الطلاب'!H401</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC403">
+        <f>'معلومات الطلاب'!H402</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC404">
+        <f>'معلومات الطلاب'!H403</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC405">
+        <f>'معلومات الطلاب'!H404</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC406">
+        <f>'معلومات الطلاب'!H405</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC407">
+        <f>'معلومات الطلاب'!H406</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC408">
+        <f>'معلومات الطلاب'!H407</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC409">
+        <f>'معلومات الطلاب'!H408</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC410">
+        <f>'معلومات الطلاب'!H409</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC411">
+        <f>'معلومات الطلاب'!H410</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2854,7 +5440,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:AG37"/>
+  <dimension ref="A2:AG411"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.33203125" customWidth="1"/>
@@ -2997,7 +5583,9 @@
       <c r="AB3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC3" s="1"/>
+      <c r="AC3" s="13" t="s">
+        <v>57</v>
+      </c>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -3098,6 +5686,10 @@
         <f>IF(Z4&lt;0.6,"متعثر",IF(Z4&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
         <v>لا يحتاج متابعة</v>
       </c>
+      <c r="AC4" t="str">
+        <f>'معلومات الطلاب'!H4</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -3194,6 +5786,10 @@
         <f t="shared" ref="AB5:AB13" si="3">IF(Z5&lt;0.6,"متعثر",IF(Z5&lt;0.8,"محتاج متابعة","لا يحتاج متابعة"))</f>
         <v>لا يحتاج متابعة</v>
       </c>
+      <c r="AC5" t="str">
+        <f>'معلومات الطلاب'!H5</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -3290,6 +5886,10 @@
         <f t="shared" si="3"/>
         <v>لا يحتاج متابعة</v>
       </c>
+      <c r="AC6" t="str">
+        <f>'معلومات الطلاب'!H6</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -3386,6 +5986,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC7" t="str">
+        <f>'معلومات الطلاب'!H7</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="8" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -3482,6 +6086,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC8" t="str">
+        <f>'معلومات الطلاب'!H8</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="9" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -3578,6 +6186,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC9" t="str">
+        <f>'معلومات الطلاب'!H9</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -3674,6 +6286,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC10" t="str">
+        <f>'معلومات الطلاب'!H10</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -3770,6 +6386,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC11" t="str">
+        <f>'معلومات الطلاب'!H11</f>
+        <v>تحفيظ</v>
+      </c>
     </row>
     <row r="12" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -3866,6 +6486,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC12" t="str">
+        <f>'معلومات الطلاب'!H12</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -3962,6 +6586,10 @@
         <f t="shared" si="3"/>
         <v>محتاج متابعة</v>
       </c>
+      <c r="AC13" t="str">
+        <f>'معلومات الطلاب'!H13</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -3984,6 +6612,10 @@
         <f>'معلومات الطلاب'!F13</f>
         <v>علوم</v>
       </c>
+      <c r="AC14" t="str">
+        <f>'معلومات الطلاب'!H14</f>
+        <v>عام</v>
+      </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -4006,6 +6638,10 @@
         <f>'معلومات الطلاب'!F14</f>
         <v>لغتي</v>
       </c>
+      <c r="AC15">
+        <f>'معلومات الطلاب'!H15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -4028,8 +6664,12 @@
         <f>'معلومات الطلاب'!F16</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC16">
+        <f>'معلومات الطلاب'!H16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>'معلومات الطلاب'!A17</f>
         <v>0</v>
@@ -4050,8 +6690,12 @@
         <f>'معلومات الطلاب'!F17</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC17">
+        <f>'معلومات الطلاب'!H17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>'معلومات الطلاب'!A18</f>
         <v>0</v>
@@ -4072,8 +6716,12 @@
         <f>'معلومات الطلاب'!F18</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC18">
+        <f>'معلومات الطلاب'!H18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>'معلومات الطلاب'!A19</f>
         <v>0</v>
@@ -4094,8 +6742,12 @@
         <f>'معلومات الطلاب'!F19</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC19">
+        <f>'معلومات الطلاب'!H19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>'معلومات الطلاب'!A20</f>
         <v>0</v>
@@ -4116,8 +6768,12 @@
         <f>'معلومات الطلاب'!F20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC20">
+        <f>'معلومات الطلاب'!H20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>'معلومات الطلاب'!A21</f>
         <v>0</v>
@@ -4138,8 +6794,12 @@
         <f>'معلومات الطلاب'!F21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC21">
+        <f>'معلومات الطلاب'!H21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>'معلومات الطلاب'!A22</f>
         <v>0</v>
@@ -4160,8 +6820,12 @@
         <f>'معلومات الطلاب'!F22</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC22">
+        <f>'معلومات الطلاب'!H22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>'معلومات الطلاب'!A23</f>
         <v>0</v>
@@ -4182,8 +6846,12 @@
         <f>'معلومات الطلاب'!F23</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC23">
+        <f>'معلومات الطلاب'!H23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>'معلومات الطلاب'!A24</f>
         <v>0</v>
@@ -4204,8 +6872,12 @@
         <f>'معلومات الطلاب'!F24</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="AC24">
+        <f>'معلومات الطلاب'!H24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>'معلومات الطلاب'!A25</f>
         <v>0</v>
@@ -4226,8 +6898,12 @@
         <f>'معلومات الطلاب'!F25</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC25">
+        <f>'معلومات الطلاب'!H25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <f>'معلومات الطلاب'!A26</f>
         <v>0</v>
@@ -4248,8 +6924,12 @@
         <f>'معلومات الطلاب'!F26</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC26">
+        <f>'معلومات الطلاب'!H26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <f>'معلومات الطلاب'!A27</f>
         <v>0</v>
@@ -4280,8 +6960,12 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC27">
+        <f>'معلومات الطلاب'!H27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -4292,8 +6976,12 @@
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC28">
+        <f>'معلومات الطلاب'!H28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -4304,8 +6992,12 @@
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC29">
+        <f>'معلومات الطلاب'!H29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -4316,8 +7008,12 @@
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC30">
+        <f>'معلومات الطلاب'!H30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4328,8 +7024,12 @@
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC31">
+        <f>'معلومات الطلاب'!H31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -4340,8 +7040,12 @@
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC32">
+        <f>'معلومات الطلاب'!H32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -4352,8 +7056,12 @@
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC33">
+        <f>'معلومات الطلاب'!H33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -4364,8 +7072,12 @@
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC34">
+        <f>'معلومات الطلاب'!H34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -4376,8 +7088,12 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC35">
+        <f>'معلومات الطلاب'!H35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -4388,8 +7104,12 @@
       <c r="U36" s="2"/>
       <c r="V36" s="2"/>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="14:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AC36">
+        <f>'معلومات الطلاب'!H36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="14:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -4400,6 +7120,2254 @@
       <c r="U37" s="2"/>
       <c r="V37" s="2"/>
       <c r="W37" s="2"/>
+      <c r="AC37">
+        <f>'معلومات الطلاب'!H37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC38">
+        <f>'معلومات الطلاب'!H38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC39">
+        <f>'معلومات الطلاب'!H39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC40">
+        <f>'معلومات الطلاب'!H40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC41">
+        <f>'معلومات الطلاب'!H41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC42">
+        <f>'معلومات الطلاب'!H42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC43">
+        <f>'معلومات الطلاب'!H43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC44">
+        <f>'معلومات الطلاب'!H44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC45">
+        <f>'معلومات الطلاب'!H45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC46">
+        <f>'معلومات الطلاب'!H46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC47">
+        <f>'معلومات الطلاب'!H47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="14:29" x14ac:dyDescent="0.3">
+      <c r="AC48">
+        <f>'معلومات الطلاب'!H48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC49">
+        <f>'معلومات الطلاب'!H49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC50">
+        <f>'معلومات الطلاب'!H50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC51">
+        <f>'معلومات الطلاب'!H51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC52">
+        <f>'معلومات الطلاب'!H52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC53">
+        <f>'معلومات الطلاب'!H53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC54">
+        <f>'معلومات الطلاب'!H54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC55">
+        <f>'معلومات الطلاب'!H55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC56">
+        <f>'معلومات الطلاب'!H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC57">
+        <f>'معلومات الطلاب'!H57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC58">
+        <f>'معلومات الطلاب'!H58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC59">
+        <f>'معلومات الطلاب'!H59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC60">
+        <f>'معلومات الطلاب'!H60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC61">
+        <f>'معلومات الطلاب'!H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC62">
+        <f>'معلومات الطلاب'!H62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC63">
+        <f>'معلومات الطلاب'!H63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC64">
+        <f>'معلومات الطلاب'!H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC65">
+        <f>'معلومات الطلاب'!H65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC66">
+        <f>'معلومات الطلاب'!H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC67">
+        <f>'معلومات الطلاب'!H67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC68">
+        <f>'معلومات الطلاب'!H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC69">
+        <f>'معلومات الطلاب'!H69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC70">
+        <f>'معلومات الطلاب'!H70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC71">
+        <f>'معلومات الطلاب'!H71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC72">
+        <f>'معلومات الطلاب'!H72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC73">
+        <f>'معلومات الطلاب'!H73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC74">
+        <f>'معلومات الطلاب'!H74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC75">
+        <f>'معلومات الطلاب'!H75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC76">
+        <f>'معلومات الطلاب'!H76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC77">
+        <f>'معلومات الطلاب'!H77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC78">
+        <f>'معلومات الطلاب'!H78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC79">
+        <f>'معلومات الطلاب'!H79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC80">
+        <f>'معلومات الطلاب'!H80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC81">
+        <f>'معلومات الطلاب'!H81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC82">
+        <f>'معلومات الطلاب'!H82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC83">
+        <f>'معلومات الطلاب'!H83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC84">
+        <f>'معلومات الطلاب'!H84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC85">
+        <f>'معلومات الطلاب'!H85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC86">
+        <f>'معلومات الطلاب'!H86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC87">
+        <f>'معلومات الطلاب'!H87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC88">
+        <f>'معلومات الطلاب'!H88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC89">
+        <f>'معلومات الطلاب'!H89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC90">
+        <f>'معلومات الطلاب'!H90</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC91">
+        <f>'معلومات الطلاب'!H91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC92">
+        <f>'معلومات الطلاب'!H92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC93">
+        <f>'معلومات الطلاب'!H93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC94">
+        <f>'معلومات الطلاب'!H94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC95">
+        <f>'معلومات الطلاب'!H95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC96">
+        <f>'معلومات الطلاب'!H96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC97">
+        <f>'معلومات الطلاب'!H97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC98">
+        <f>'معلومات الطلاب'!H98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC99">
+        <f>'معلومات الطلاب'!H99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC100">
+        <f>'معلومات الطلاب'!H100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC101">
+        <f>'معلومات الطلاب'!H101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC102">
+        <f>'معلومات الطلاب'!H102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC103">
+        <f>'معلومات الطلاب'!H103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC104">
+        <f>'معلومات الطلاب'!H104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC105">
+        <f>'معلومات الطلاب'!H105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC106">
+        <f>'معلومات الطلاب'!H106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC107">
+        <f>'معلومات الطلاب'!H107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC108">
+        <f>'معلومات الطلاب'!H108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC109">
+        <f>'معلومات الطلاب'!H109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC110">
+        <f>'معلومات الطلاب'!H110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC111">
+        <f>'معلومات الطلاب'!H111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC112">
+        <f>'معلومات الطلاب'!H112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC113">
+        <f>'معلومات الطلاب'!H113</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC114">
+        <f>'معلومات الطلاب'!H114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC115">
+        <f>'معلومات الطلاب'!H115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC116">
+        <f>'معلومات الطلاب'!H116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC117">
+        <f>'معلومات الطلاب'!H117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC118">
+        <f>'معلومات الطلاب'!H118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC119">
+        <f>'معلومات الطلاب'!H119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC120">
+        <f>'معلومات الطلاب'!H120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC121">
+        <f>'معلومات الطلاب'!H121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC122">
+        <f>'معلومات الطلاب'!H122</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC123">
+        <f>'معلومات الطلاب'!H123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC124">
+        <f>'معلومات الطلاب'!H124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC125">
+        <f>'معلومات الطلاب'!H125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC126">
+        <f>'معلومات الطلاب'!H126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC127">
+        <f>'معلومات الطلاب'!H127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC128">
+        <f>'معلومات الطلاب'!H128</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC129">
+        <f>'معلومات الطلاب'!H129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC130">
+        <f>'معلومات الطلاب'!H130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC131">
+        <f>'معلومات الطلاب'!H131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC132">
+        <f>'معلومات الطلاب'!H132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC133">
+        <f>'معلومات الطلاب'!H133</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC134">
+        <f>'معلومات الطلاب'!H134</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC135">
+        <f>'معلومات الطلاب'!H135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC136">
+        <f>'معلومات الطلاب'!H136</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC137">
+        <f>'معلومات الطلاب'!H137</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC138">
+        <f>'معلومات الطلاب'!H138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC139">
+        <f>'معلومات الطلاب'!H139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC140">
+        <f>'معلومات الطلاب'!H140</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC141">
+        <f>'معلومات الطلاب'!H141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC142">
+        <f>'معلومات الطلاب'!H142</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC143">
+        <f>'معلومات الطلاب'!H143</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC144">
+        <f>'معلومات الطلاب'!H144</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC145">
+        <f>'معلومات الطلاب'!H145</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC146">
+        <f>'معلومات الطلاب'!H146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC147">
+        <f>'معلومات الطلاب'!H147</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC148">
+        <f>'معلومات الطلاب'!H148</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC149">
+        <f>'معلومات الطلاب'!H149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC150">
+        <f>'معلومات الطلاب'!H150</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC151">
+        <f>'معلومات الطلاب'!H151</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC152">
+        <f>'معلومات الطلاب'!H152</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC153">
+        <f>'معلومات الطلاب'!H153</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC154">
+        <f>'معلومات الطلاب'!H154</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC155">
+        <f>'معلومات الطلاب'!H155</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC156">
+        <f>'معلومات الطلاب'!H156</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC157">
+        <f>'معلومات الطلاب'!H157</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC158">
+        <f>'معلومات الطلاب'!H158</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC159">
+        <f>'معلومات الطلاب'!H159</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC160">
+        <f>'معلومات الطلاب'!H160</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC161">
+        <f>'معلومات الطلاب'!H161</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC162">
+        <f>'معلومات الطلاب'!H162</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC163">
+        <f>'معلومات الطلاب'!H163</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC164">
+        <f>'معلومات الطلاب'!H164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC165">
+        <f>'معلومات الطلاب'!H165</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC166">
+        <f>'معلومات الطلاب'!H166</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC167">
+        <f>'معلومات الطلاب'!H167</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC168">
+        <f>'معلومات الطلاب'!H168</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC169">
+        <f>'معلومات الطلاب'!H169</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC170">
+        <f>'معلومات الطلاب'!H170</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC171">
+        <f>'معلومات الطلاب'!H171</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC172">
+        <f>'معلومات الطلاب'!H172</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC173">
+        <f>'معلومات الطلاب'!H173</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC174">
+        <f>'معلومات الطلاب'!H174</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC175">
+        <f>'معلومات الطلاب'!H175</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC176">
+        <f>'معلومات الطلاب'!H176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC177">
+        <f>'معلومات الطلاب'!H177</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC178">
+        <f>'معلومات الطلاب'!H178</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC179">
+        <f>'معلومات الطلاب'!H179</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC180">
+        <f>'معلومات الطلاب'!H180</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC181">
+        <f>'معلومات الطلاب'!H181</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC182">
+        <f>'معلومات الطلاب'!H182</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC183">
+        <f>'معلومات الطلاب'!H183</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC184">
+        <f>'معلومات الطلاب'!H184</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC185">
+        <f>'معلومات الطلاب'!H185</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC186">
+        <f>'معلومات الطلاب'!H186</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC187">
+        <f>'معلومات الطلاب'!H187</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC188">
+        <f>'معلومات الطلاب'!H188</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC189">
+        <f>'معلومات الطلاب'!H189</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC190">
+        <f>'معلومات الطلاب'!H190</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC191">
+        <f>'معلومات الطلاب'!H191</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC192">
+        <f>'معلومات الطلاب'!H192</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC193">
+        <f>'معلومات الطلاب'!H193</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC194">
+        <f>'معلومات الطلاب'!H194</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC195">
+        <f>'معلومات الطلاب'!H195</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC196">
+        <f>'معلومات الطلاب'!H196</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC197">
+        <f>'معلومات الطلاب'!H197</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC198">
+        <f>'معلومات الطلاب'!H198</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC199">
+        <f>'معلومات الطلاب'!H199</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC200">
+        <f>'معلومات الطلاب'!H200</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC201">
+        <f>'معلومات الطلاب'!H201</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC202">
+        <f>'معلومات الطلاب'!H202</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC203">
+        <f>'معلومات الطلاب'!H203</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC204">
+        <f>'معلومات الطلاب'!H204</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC205">
+        <f>'معلومات الطلاب'!H205</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC206">
+        <f>'معلومات الطلاب'!H206</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC207">
+        <f>'معلومات الطلاب'!H207</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC208">
+        <f>'معلومات الطلاب'!H208</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC209">
+        <f>'معلومات الطلاب'!H209</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC210">
+        <f>'معلومات الطلاب'!H210</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC211">
+        <f>'معلومات الطلاب'!H211</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC212">
+        <f>'معلومات الطلاب'!H212</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC213">
+        <f>'معلومات الطلاب'!H213</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC214">
+        <f>'معلومات الطلاب'!H214</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC215">
+        <f>'معلومات الطلاب'!H215</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC216">
+        <f>'معلومات الطلاب'!H216</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC217">
+        <f>'معلومات الطلاب'!H217</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC218">
+        <f>'معلومات الطلاب'!H218</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC219">
+        <f>'معلومات الطلاب'!H219</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC220">
+        <f>'معلومات الطلاب'!H220</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC221">
+        <f>'معلومات الطلاب'!H221</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC222">
+        <f>'معلومات الطلاب'!H222</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC223">
+        <f>'معلومات الطلاب'!H223</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC224">
+        <f>'معلومات الطلاب'!H224</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC225">
+        <f>'معلومات الطلاب'!H225</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC226">
+        <f>'معلومات الطلاب'!H226</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC227">
+        <f>'معلومات الطلاب'!H227</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC228">
+        <f>'معلومات الطلاب'!H228</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC229">
+        <f>'معلومات الطلاب'!H229</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC230">
+        <f>'معلومات الطلاب'!H230</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC231">
+        <f>'معلومات الطلاب'!H231</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC232">
+        <f>'معلومات الطلاب'!H232</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC233">
+        <f>'معلومات الطلاب'!H233</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC234">
+        <f>'معلومات الطلاب'!H234</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC235">
+        <f>'معلومات الطلاب'!H235</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC236">
+        <f>'معلومات الطلاب'!H236</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC237">
+        <f>'معلومات الطلاب'!H237</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC238">
+        <f>'معلومات الطلاب'!H238</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC239">
+        <f>'معلومات الطلاب'!H239</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC240">
+        <f>'معلومات الطلاب'!H240</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC241">
+        <f>'معلومات الطلاب'!H241</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC242">
+        <f>'معلومات الطلاب'!H242</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC243">
+        <f>'معلومات الطلاب'!H243</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC244">
+        <f>'معلومات الطلاب'!H244</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC245">
+        <f>'معلومات الطلاب'!H245</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC246">
+        <f>'معلومات الطلاب'!H246</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC247">
+        <f>'معلومات الطلاب'!H247</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC248">
+        <f>'معلومات الطلاب'!H248</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC249">
+        <f>'معلومات الطلاب'!H249</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC250">
+        <f>'معلومات الطلاب'!H250</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC251">
+        <f>'معلومات الطلاب'!H251</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC252">
+        <f>'معلومات الطلاب'!H252</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC253">
+        <f>'معلومات الطلاب'!H253</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC254">
+        <f>'معلومات الطلاب'!H254</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC255">
+        <f>'معلومات الطلاب'!H255</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC256">
+        <f>'معلومات الطلاب'!H256</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC257">
+        <f>'معلومات الطلاب'!H257</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC258">
+        <f>'معلومات الطلاب'!H258</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC259">
+        <f>'معلومات الطلاب'!H259</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC260">
+        <f>'معلومات الطلاب'!H260</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC261">
+        <f>'معلومات الطلاب'!H261</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC262">
+        <f>'معلومات الطلاب'!H262</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC263">
+        <f>'معلومات الطلاب'!H263</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC264">
+        <f>'معلومات الطلاب'!H264</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC265">
+        <f>'معلومات الطلاب'!H265</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC266">
+        <f>'معلومات الطلاب'!H266</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC267">
+        <f>'معلومات الطلاب'!H267</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC268">
+        <f>'معلومات الطلاب'!H268</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC269">
+        <f>'معلومات الطلاب'!H269</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC270">
+        <f>'معلومات الطلاب'!H270</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC271">
+        <f>'معلومات الطلاب'!H271</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC272">
+        <f>'معلومات الطلاب'!H272</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC273">
+        <f>'معلومات الطلاب'!H273</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC274">
+        <f>'معلومات الطلاب'!H274</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC275">
+        <f>'معلومات الطلاب'!H275</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC276">
+        <f>'معلومات الطلاب'!H276</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC277">
+        <f>'معلومات الطلاب'!H277</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC278">
+        <f>'معلومات الطلاب'!H278</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC279">
+        <f>'معلومات الطلاب'!H279</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC280">
+        <f>'معلومات الطلاب'!H280</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC281">
+        <f>'معلومات الطلاب'!H281</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC282">
+        <f>'معلومات الطلاب'!H282</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC283">
+        <f>'معلومات الطلاب'!H283</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC284">
+        <f>'معلومات الطلاب'!H284</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC285">
+        <f>'معلومات الطلاب'!H285</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC286">
+        <f>'معلومات الطلاب'!H286</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC287">
+        <f>'معلومات الطلاب'!H287</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC288">
+        <f>'معلومات الطلاب'!H288</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC289">
+        <f>'معلومات الطلاب'!H289</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC290">
+        <f>'معلومات الطلاب'!H290</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC291">
+        <f>'معلومات الطلاب'!H291</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC292">
+        <f>'معلومات الطلاب'!H292</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC293">
+        <f>'معلومات الطلاب'!H293</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC294">
+        <f>'معلومات الطلاب'!H294</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC295">
+        <f>'معلومات الطلاب'!H295</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC296">
+        <f>'معلومات الطلاب'!H296</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC297">
+        <f>'معلومات الطلاب'!H297</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC298">
+        <f>'معلومات الطلاب'!H298</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC299">
+        <f>'معلومات الطلاب'!H299</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC300">
+        <f>'معلومات الطلاب'!H300</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC301">
+        <f>'معلومات الطلاب'!H301</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC302">
+        <f>'معلومات الطلاب'!H302</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC303">
+        <f>'معلومات الطلاب'!H303</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC304">
+        <f>'معلومات الطلاب'!H304</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC305">
+        <f>'معلومات الطلاب'!H305</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC306">
+        <f>'معلومات الطلاب'!H306</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC307">
+        <f>'معلومات الطلاب'!H307</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC308">
+        <f>'معلومات الطلاب'!H308</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC309">
+        <f>'معلومات الطلاب'!H309</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC310">
+        <f>'معلومات الطلاب'!H310</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC311">
+        <f>'معلومات الطلاب'!H311</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC312">
+        <f>'معلومات الطلاب'!H312</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC313">
+        <f>'معلومات الطلاب'!H313</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC314">
+        <f>'معلومات الطلاب'!H314</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC315">
+        <f>'معلومات الطلاب'!H315</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC316">
+        <f>'معلومات الطلاب'!H316</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC317">
+        <f>'معلومات الطلاب'!H317</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC318">
+        <f>'معلومات الطلاب'!H318</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC319">
+        <f>'معلومات الطلاب'!H319</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC320">
+        <f>'معلومات الطلاب'!H320</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC321">
+        <f>'معلومات الطلاب'!H321</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC322">
+        <f>'معلومات الطلاب'!H322</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC323">
+        <f>'معلومات الطلاب'!H323</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC324">
+        <f>'معلومات الطلاب'!H324</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC325">
+        <f>'معلومات الطلاب'!H325</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC326">
+        <f>'معلومات الطلاب'!H326</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC327">
+        <f>'معلومات الطلاب'!H327</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC328">
+        <f>'معلومات الطلاب'!H328</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC329">
+        <f>'معلومات الطلاب'!H329</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC330">
+        <f>'معلومات الطلاب'!H330</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC331">
+        <f>'معلومات الطلاب'!H331</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC332">
+        <f>'معلومات الطلاب'!H332</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC333">
+        <f>'معلومات الطلاب'!H333</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC334">
+        <f>'معلومات الطلاب'!H334</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC335">
+        <f>'معلومات الطلاب'!H335</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC336">
+        <f>'معلومات الطلاب'!H336</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC337">
+        <f>'معلومات الطلاب'!H337</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC338">
+        <f>'معلومات الطلاب'!H338</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC339">
+        <f>'معلومات الطلاب'!H339</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC340">
+        <f>'معلومات الطلاب'!H340</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC341">
+        <f>'معلومات الطلاب'!H341</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC342">
+        <f>'معلومات الطلاب'!H342</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC343">
+        <f>'معلومات الطلاب'!H343</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC344">
+        <f>'معلومات الطلاب'!H344</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC345">
+        <f>'معلومات الطلاب'!H345</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC346">
+        <f>'معلومات الطلاب'!H346</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC347">
+        <f>'معلومات الطلاب'!H347</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC348">
+        <f>'معلومات الطلاب'!H348</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC349">
+        <f>'معلومات الطلاب'!H349</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC350">
+        <f>'معلومات الطلاب'!H350</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC351">
+        <f>'معلومات الطلاب'!H351</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC352">
+        <f>'معلومات الطلاب'!H352</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC353">
+        <f>'معلومات الطلاب'!H353</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC354">
+        <f>'معلومات الطلاب'!H354</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC355">
+        <f>'معلومات الطلاب'!H355</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC356">
+        <f>'معلومات الطلاب'!H356</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC357">
+        <f>'معلومات الطلاب'!H357</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC358">
+        <f>'معلومات الطلاب'!H358</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC359">
+        <f>'معلومات الطلاب'!H359</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC360">
+        <f>'معلومات الطلاب'!H360</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC361">
+        <f>'معلومات الطلاب'!H361</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC362">
+        <f>'معلومات الطلاب'!H362</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC363">
+        <f>'معلومات الطلاب'!H363</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC364">
+        <f>'معلومات الطلاب'!H364</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC365">
+        <f>'معلومات الطلاب'!H365</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC366">
+        <f>'معلومات الطلاب'!H366</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC367">
+        <f>'معلومات الطلاب'!H367</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC368">
+        <f>'معلومات الطلاب'!H368</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC369">
+        <f>'معلومات الطلاب'!H369</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC370">
+        <f>'معلومات الطلاب'!H370</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC371">
+        <f>'معلومات الطلاب'!H371</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC372">
+        <f>'معلومات الطلاب'!H372</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC373">
+        <f>'معلومات الطلاب'!H373</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC374">
+        <f>'معلومات الطلاب'!H374</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC375">
+        <f>'معلومات الطلاب'!H375</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC376">
+        <f>'معلومات الطلاب'!H376</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC377">
+        <f>'معلومات الطلاب'!H377</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC378">
+        <f>'معلومات الطلاب'!H378</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC379">
+        <f>'معلومات الطلاب'!H379</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC380">
+        <f>'معلومات الطلاب'!H380</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC381">
+        <f>'معلومات الطلاب'!H381</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC382">
+        <f>'معلومات الطلاب'!H382</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC383">
+        <f>'معلومات الطلاب'!H383</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC384">
+        <f>'معلومات الطلاب'!H384</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC385">
+        <f>'معلومات الطلاب'!H385</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC386">
+        <f>'معلومات الطلاب'!H386</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC387">
+        <f>'معلومات الطلاب'!H387</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC388">
+        <f>'معلومات الطلاب'!H388</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC389">
+        <f>'معلومات الطلاب'!H389</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC390">
+        <f>'معلومات الطلاب'!H390</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC391">
+        <f>'معلومات الطلاب'!H391</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC392">
+        <f>'معلومات الطلاب'!H392</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC393">
+        <f>'معلومات الطلاب'!H393</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC394">
+        <f>'معلومات الطلاب'!H394</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC395">
+        <f>'معلومات الطلاب'!H395</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC396">
+        <f>'معلومات الطلاب'!H396</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC397">
+        <f>'معلومات الطلاب'!H397</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC398">
+        <f>'معلومات الطلاب'!H398</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC399">
+        <f>'معلومات الطلاب'!H399</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC400">
+        <f>'معلومات الطلاب'!H400</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC401">
+        <f>'معلومات الطلاب'!H401</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC402">
+        <f>'معلومات الطلاب'!H402</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC403">
+        <f>'معلومات الطلاب'!H403</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC404">
+        <f>'معلومات الطلاب'!H404</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC405">
+        <f>'معلومات الطلاب'!H405</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC406">
+        <f>'معلومات الطلاب'!H406</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC407">
+        <f>'معلومات الطلاب'!H407</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC408">
+        <f>'معلومات الطلاب'!H408</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC409">
+        <f>'معلومات الطلاب'!H409</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC410">
+        <f>'معلومات الطلاب'!H410</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="29:29" x14ac:dyDescent="0.3">
+      <c r="AC411">
+        <f>'معلومات الطلاب'!H411</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
